--- a/branches/master/StructureDefinition-mii-pr-labor-laborbefund.xlsx
+++ b/branches/master/StructureDefinition-mii-pr-labor-laborbefund.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T16:29:24+00:00</t>
+    <t>2026-09-02T07:15:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-mii-pr-labor-laborbefund.xlsx
+++ b/branches/master/StructureDefinition-mii-pr-labor-laborbefund.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T07:15:34+00:00</t>
+    <t>2026-09-02T11:58:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-mii-pr-labor-laborbefund.xlsx
+++ b/branches/master/StructureDefinition-mii-pr-labor-laborbefund.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0</t>
+    <t>2027.0.0-ballot.rc1</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T11:58:19+00:00</t>
+    <t>2026-09-02T12:35:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-mii-pr-labor-laborbefund.xlsx
+++ b/branches/master/StructureDefinition-mii-pr-labor-laborbefund.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T12:35:29+00:00</t>
+    <t>2026-09-02T13:24:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-mii-pr-labor-laborbefund.xlsx
+++ b/branches/master/StructureDefinition-mii-pr-labor-laborbefund.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AM$127</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AM$128</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4498" uniqueCount="585">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4533" uniqueCount="594">
   <si>
     <t>Property</t>
   </si>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T13:24:46+00:00</t>
+    <t>2026-09-02T15:00:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1210,29 +1210,58 @@
     <t>http://hl7.org/fhir/ValueSet/diagnostic-service-sections|4.0.1</t>
   </si>
   <si>
-    <t>OBR-24</t>
-  </si>
-  <si>
-    <t>FiveWs.class</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.category.id</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.category.extension</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.category.coding</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
     <t xml:space="preserve">pattern:$this}
 </t>
   </si>
   <si>
-    <t>DiagnosticReport.category.coding:loinc-lab</t>
+    <t>OBR-24</t>
+  </si>
+  <si>
+    <t>FiveWs.class</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.category:laborbefund</t>
+  </si>
+  <si>
+    <t>laborbefund</t>
+  </si>
+  <si>
+    <t>Laborbefund-Kategorie</t>
+  </si>
+  <si>
+    <t>Die verpflichtende Kategorie des Laborbefunds. Weitere Kategorien, etwa der Laborbereich, sind als zusaetzliche category-Eintraege zulaessig.</t>
+  </si>
+  <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="http://loinc.org"/&gt;
+    &lt;code value="26436-6"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.category:laborbefund.id</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.category.id</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.category:laborbefund.extension</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.category.extension</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.category:laborbefund.coding</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.category.coding</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.category:laborbefund.coding:loinc-lab</t>
   </si>
   <si>
     <t>loinc-lab</t>
@@ -1244,7 +1273,7 @@
 &lt;/valueCoding&gt;</t>
   </si>
   <si>
-    <t>DiagnosticReport.category.coding:diagnostic-service-sections</t>
+    <t>DiagnosticReport.category:laborbefund.coding:diagnostic-service-sections</t>
   </si>
   <si>
     <t>diagnostic-service-sections</t>
@@ -1254,6 +1283,9 @@
   &lt;system value="http://terminology.hl7.org/CodeSystem/v2-0074"/&gt;
   &lt;code value="LAB"/&gt;
 &lt;/valueCoding&gt;</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.category:laborbefund.text</t>
   </si>
   <si>
     <t>DiagnosticReport.category.text</t>
@@ -2171,10 +2203,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AM127"/>
+  <dimension ref="A1:AM128"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="56.33984375" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="59.58203125" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="42.53515625" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="24.5234375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="53.34375" customWidth="true" bestFit="true" hidden="true"/>
@@ -7560,7 +7592,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
         <v>376</v>
       </c>
@@ -7635,16 +7667,14 @@
         <v>79</v>
       </c>
       <c r="AB49" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC49" t="s" s="2">
-        <v>79</v>
-      </c>
+        <v>383</v>
+      </c>
+      <c r="AC49" s="2"/>
       <c r="AD49" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE49" t="s" s="2">
-        <v>79</v>
+        <v>114</v>
       </c>
       <c r="AF49" t="s" s="2">
         <v>376</v>
@@ -7665,49 +7695,53 @@
         <v>79</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
-    <row r="50" hidden="true">
+    <row r="50">
       <c r="A50" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>385</v>
-      </c>
-      <c r="C50" s="2"/>
+        <v>376</v>
+      </c>
+      <c r="C50" t="s" s="2">
+        <v>387</v>
+      </c>
       <c r="D50" t="s" s="2">
-        <v>79</v>
+        <v>377</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="G50" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H50" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="I50" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>102</v>
+        <v>225</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>103</v>
+        <v>388</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="N50" s="2"/>
+        <v>389</v>
+      </c>
+      <c r="N50" t="s" s="2">
+        <v>380</v>
+      </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>79</v>
@@ -7717,7 +7751,7 @@
         <v>79</v>
       </c>
       <c r="S50" t="s" s="2">
-        <v>79</v>
+        <v>390</v>
       </c>
       <c r="T50" t="s" s="2">
         <v>79</v>
@@ -7732,13 +7766,13 @@
         <v>79</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>79</v>
+        <v>153</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>79</v>
+        <v>381</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>79</v>
+        <v>382</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>79</v>
@@ -7756,47 +7790,47 @@
         <v>79</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>105</v>
+        <v>376</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>79</v>
+        <v>384</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>79</v>
+        <v>385</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>107</v>
+        <v>79</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>79</v>
@@ -7808,17 +7842,15 @@
         <v>79</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>111</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="N51" s="2"/>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>79</v>
@@ -7855,31 +7887,31 @@
         <v>79</v>
       </c>
       <c r="AB51" t="s" s="2">
-        <v>112</v>
+        <v>79</v>
       </c>
       <c r="AC51" t="s" s="2">
-        <v>113</v>
+        <v>79</v>
       </c>
       <c r="AD51" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE51" t="s" s="2">
-        <v>114</v>
+        <v>79</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>116</v>
+        <v>79</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>79</v>
@@ -7893,18 +7925,18 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>387</v>
+        <v>393</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>387</v>
+        <v>394</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>79</v>
+        <v>107</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>388</v>
+        <v>77</v>
       </c>
       <c r="G52" t="s" s="2">
         <v>78</v>
@@ -7916,23 +7948,21 @@
         <v>79</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>141</v>
+        <v>108</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>241</v>
+        <v>109</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>242</v>
+        <v>110</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>243</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>244</v>
-      </c>
+        <v>111</v>
+      </c>
+      <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>79</v>
       </c>
@@ -7968,9 +7998,11 @@
         <v>79</v>
       </c>
       <c r="AB52" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="AC52" s="2"/>
+        <v>112</v>
+      </c>
+      <c r="AC52" t="s" s="2">
+        <v>113</v>
+      </c>
       <c r="AD52" t="s" s="2">
         <v>79</v>
       </c>
@@ -7978,7 +8010,7 @@
         <v>114</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>246</v>
+        <v>115</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>77</v>
@@ -7990,40 +8022,38 @@
         <v>79</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>100</v>
+        <v>116</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>247</v>
+        <v>79</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>79</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>387</v>
-      </c>
-      <c r="C53" t="s" s="2">
-        <v>391</v>
-      </c>
+        <v>396</v>
+      </c>
+      <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
         <v>79</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
-        <v>88</v>
+        <v>397</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H53" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="I53" t="s" s="2">
         <v>79</v>
@@ -8054,7 +8084,7 @@
         <v>79</v>
       </c>
       <c r="S53" t="s" s="2">
-        <v>392</v>
+        <v>79</v>
       </c>
       <c r="T53" t="s" s="2">
         <v>79</v>
@@ -8081,16 +8111,14 @@
         <v>79</v>
       </c>
       <c r="AB53" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC53" t="s" s="2">
-        <v>79</v>
-      </c>
+        <v>383</v>
+      </c>
+      <c r="AC53" s="2"/>
       <c r="AD53" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE53" t="s" s="2">
-        <v>79</v>
+        <v>114</v>
       </c>
       <c r="AF53" t="s" s="2">
         <v>246</v>
@@ -8119,13 +8147,13 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>387</v>
+        <v>396</v>
       </c>
       <c r="C54" t="s" s="2">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="D54" t="s" s="2">
         <v>79</v>
@@ -8169,7 +8197,7 @@
         <v>79</v>
       </c>
       <c r="S54" t="s" s="2">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="T54" t="s" s="2">
         <v>79</v>
@@ -8232,26 +8260,28 @@
         <v>79</v>
       </c>
     </row>
-    <row r="55" hidden="true">
+    <row r="55">
       <c r="A55" t="s" s="2">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="B55" t="s" s="2">
         <v>396</v>
       </c>
-      <c r="C55" s="2"/>
+      <c r="C55" t="s" s="2">
+        <v>402</v>
+      </c>
       <c r="D55" t="s" s="2">
         <v>79</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="G55" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H55" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="I55" t="s" s="2">
         <v>79</v>
@@ -8260,19 +8290,19 @@
         <v>89</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>296</v>
+        <v>241</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>297</v>
+        <v>242</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>298</v>
+        <v>243</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>299</v>
+        <v>244</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>79</v>
@@ -8282,7 +8312,7 @@
         <v>79</v>
       </c>
       <c r="S55" t="s" s="2">
-        <v>79</v>
+        <v>403</v>
       </c>
       <c r="T55" t="s" s="2">
         <v>79</v>
@@ -8321,13 +8351,13 @@
         <v>79</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>300</v>
+        <v>246</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>79</v>
@@ -8339,32 +8369,32 @@
         <v>79</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>301</v>
+        <v>247</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>79</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>397</v>
+        <v>404</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>397</v>
+        <v>405</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>398</v>
+        <v>79</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="G56" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H56" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="I56" t="s" s="2">
         <v>79</v>
@@ -8373,16 +8403,20 @@
         <v>89</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>225</v>
+        <v>102</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>63</v>
+        <v>296</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>399</v>
-      </c>
-      <c r="N56" s="2"/>
-      <c r="O56" s="2"/>
+        <v>297</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="O56" t="s" s="2">
+        <v>299</v>
+      </c>
       <c r="P56" t="s" s="2">
         <v>79</v>
       </c>
@@ -8406,13 +8440,13 @@
         <v>79</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>167</v>
+        <v>79</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>400</v>
+        <v>79</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>401</v>
+        <v>79</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>79</v>
@@ -8430,10 +8464,10 @@
         <v>79</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>397</v>
+        <v>300</v>
       </c>
       <c r="AG56" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="AH56" t="s" s="2">
         <v>88</v>
@@ -8445,50 +8479,50 @@
         <v>100</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>402</v>
+        <v>79</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>403</v>
+        <v>301</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>404</v>
+        <v>79</v>
       </c>
     </row>
-    <row r="57" hidden="true">
+    <row r="57">
       <c r="A57" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>79</v>
+        <v>407</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="G57" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H57" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="I57" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>102</v>
+        <v>225</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>103</v>
+        <v>63</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>104</v>
+        <v>408</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -8515,13 +8549,13 @@
         <v>79</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>79</v>
+        <v>167</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>79</v>
+        <v>409</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>79</v>
+        <v>410</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>79</v>
@@ -8539,10 +8573,10 @@
         <v>79</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>105</v>
+        <v>406</v>
       </c>
       <c r="AG57" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="AH57" t="s" s="2">
         <v>88</v>
@@ -8551,35 +8585,35 @@
         <v>79</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>79</v>
+        <v>411</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>79</v>
+        <v>412</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>79</v>
+        <v>413</v>
       </c>
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>406</v>
+        <v>414</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>406</v>
+        <v>414</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>107</v>
+        <v>79</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>79</v>
@@ -8591,17 +8625,15 @@
         <v>79</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>111</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="N58" s="2"/>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>79</v>
@@ -8638,31 +8670,31 @@
         <v>79</v>
       </c>
       <c r="AB58" t="s" s="2">
-        <v>112</v>
+        <v>79</v>
       </c>
       <c r="AC58" t="s" s="2">
-        <v>113</v>
+        <v>79</v>
       </c>
       <c r="AD58" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE58" t="s" s="2">
-        <v>114</v>
+        <v>79</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>116</v>
+        <v>79</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>79</v>
@@ -8676,46 +8708,44 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>407</v>
+        <v>415</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>407</v>
+        <v>415</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>79</v>
+        <v>107</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="G59" t="s" s="2">
         <v>78</v>
       </c>
       <c r="H59" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="I59" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>141</v>
+        <v>108</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>241</v>
+        <v>109</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>242</v>
+        <v>110</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>243</v>
-      </c>
-      <c r="O59" t="s" s="2">
-        <v>244</v>
-      </c>
+        <v>111</v>
+      </c>
+      <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>79</v>
       </c>
@@ -8751,9 +8781,11 @@
         <v>79</v>
       </c>
       <c r="AB59" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="AC59" s="2"/>
+        <v>112</v>
+      </c>
+      <c r="AC59" t="s" s="2">
+        <v>113</v>
+      </c>
       <c r="AD59" t="s" s="2">
         <v>79</v>
       </c>
@@ -8761,7 +8793,7 @@
         <v>114</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>246</v>
+        <v>115</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>77</v>
@@ -8773,13 +8805,13 @@
         <v>79</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>100</v>
+        <v>116</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>247</v>
+        <v>79</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>79</v>
@@ -8787,10 +8819,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>408</v>
+        <v>416</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>408</v>
+        <v>416</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8798,31 +8830,35 @@
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H60" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="I60" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>103</v>
+        <v>241</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="N60" s="2"/>
-      <c r="O60" s="2"/>
+        <v>242</v>
+      </c>
+      <c r="N60" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="O60" t="s" s="2">
+        <v>244</v>
+      </c>
       <c r="P60" t="s" s="2">
         <v>79</v>
       </c>
@@ -8858,37 +8894,35 @@
         <v>79</v>
       </c>
       <c r="AB60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC60" t="s" s="2">
-        <v>79</v>
-      </c>
+        <v>383</v>
+      </c>
+      <c r="AC60" s="2"/>
       <c r="AD60" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE60" t="s" s="2">
-        <v>79</v>
+        <v>114</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>105</v>
+        <v>246</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>79</v>
+        <v>247</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>79</v>
@@ -8896,21 +8930,21 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>107</v>
+        <v>79</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>79</v>
@@ -8922,17 +8956,15 @@
         <v>79</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>111</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="N61" s="2"/>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>79</v>
@@ -8969,31 +9001,31 @@
         <v>79</v>
       </c>
       <c r="AB61" t="s" s="2">
-        <v>112</v>
+        <v>79</v>
       </c>
       <c r="AC61" t="s" s="2">
-        <v>113</v>
+        <v>79</v>
       </c>
       <c r="AD61" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE61" t="s" s="2">
-        <v>114</v>
+        <v>79</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>116</v>
+        <v>79</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>79</v>
@@ -9005,48 +9037,46 @@
         <v>79</v>
       </c>
     </row>
-    <row r="62">
+    <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>410</v>
+        <v>418</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>410</v>
+        <v>418</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>79</v>
+        <v>107</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H62" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="I62" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>129</v>
+        <v>108</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>256</v>
+        <v>109</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>257</v>
+        <v>110</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>258</v>
-      </c>
-      <c r="O62" t="s" s="2">
-        <v>259</v>
-      </c>
+        <v>111</v>
+      </c>
+      <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>79</v>
       </c>
@@ -9082,48 +9112,48 @@
         <v>79</v>
       </c>
       <c r="AB62" t="s" s="2">
-        <v>79</v>
+        <v>112</v>
       </c>
       <c r="AC62" t="s" s="2">
-        <v>79</v>
+        <v>113</v>
       </c>
       <c r="AD62" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE62" t="s" s="2">
-        <v>79</v>
+        <v>114</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>261</v>
+        <v>115</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>100</v>
+        <v>116</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>262</v>
+        <v>79</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>79</v>
       </c>
     </row>
-    <row r="63" hidden="true">
+    <row r="63">
       <c r="A63" t="s" s="2">
-        <v>411</v>
+        <v>419</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>411</v>
+        <v>419</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9131,13 +9161,13 @@
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="G63" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H63" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="I63" t="s" s="2">
         <v>79</v>
@@ -9146,18 +9176,20 @@
         <v>89</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>102</v>
+        <v>129</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>265</v>
+        <v>256</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>266</v>
+        <v>257</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="O63" s="2"/>
+        <v>258</v>
+      </c>
+      <c r="O63" t="s" s="2">
+        <v>259</v>
+      </c>
       <c r="P63" t="s" s="2">
         <v>79</v>
       </c>
@@ -9205,7 +9237,7 @@
         <v>79</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>77</v>
@@ -9223,18 +9255,18 @@
         <v>79</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>269</v>
+        <v>262</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>79</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>412</v>
+        <v>420</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>412</v>
+        <v>420</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9242,13 +9274,13 @@
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="G64" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H64" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="I64" t="s" s="2">
         <v>79</v>
@@ -9257,18 +9289,18 @@
         <v>89</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>163</v>
+        <v>102</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="N64" s="2"/>
-      <c r="O64" t="s" s="2">
-        <v>274</v>
-      </c>
+        <v>266</v>
+      </c>
+      <c r="N64" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>79</v>
       </c>
@@ -9316,7 +9348,7 @@
         <v>79</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>77</v>
@@ -9334,7 +9366,7 @@
         <v>79</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>277</v>
+        <v>269</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>79</v>
@@ -9342,10 +9374,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>413</v>
+        <v>421</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>413</v>
+        <v>421</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9353,7 +9385,7 @@
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="G65" t="s" s="2">
         <v>88</v>
@@ -9368,17 +9400,17 @@
         <v>89</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>102</v>
+        <v>163</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>281</v>
+        <v>273</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" t="s" s="2">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>79</v>
@@ -9427,7 +9459,7 @@
         <v>79</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>77</v>
@@ -9445,18 +9477,18 @@
         <v>79</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>284</v>
+        <v>277</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>79</v>
       </c>
     </row>
-    <row r="66" hidden="true">
+    <row r="66">
       <c r="A66" t="s" s="2">
-        <v>414</v>
+        <v>422</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>414</v>
+        <v>422</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9470,7 +9502,7 @@
         <v>88</v>
       </c>
       <c r="H66" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="I66" t="s" s="2">
         <v>79</v>
@@ -9479,19 +9511,17 @@
         <v>89</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>287</v>
+        <v>102</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>288</v>
+        <v>280</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>290</v>
-      </c>
+        <v>281</v>
+      </c>
+      <c r="N66" s="2"/>
       <c r="O66" t="s" s="2">
-        <v>291</v>
+        <v>282</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>79</v>
@@ -9540,7 +9570,7 @@
         <v>79</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>292</v>
+        <v>283</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>77</v>
@@ -9558,34 +9588,32 @@
         <v>79</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>79</v>
       </c>
     </row>
-    <row r="67">
+    <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>415</v>
+        <v>423</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>407</v>
-      </c>
-      <c r="C67" t="s" s="2">
-        <v>416</v>
-      </c>
+        <v>423</v>
+      </c>
+      <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
         <v>79</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="G67" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H67" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="I67" t="s" s="2">
         <v>79</v>
@@ -9594,19 +9622,19 @@
         <v>89</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>141</v>
+        <v>287</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>241</v>
+        <v>288</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>242</v>
+        <v>289</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>243</v>
+        <v>290</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>244</v>
+        <v>291</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>79</v>
@@ -9616,7 +9644,7 @@
         <v>79</v>
       </c>
       <c r="S67" t="s" s="2">
-        <v>417</v>
+        <v>79</v>
       </c>
       <c r="T67" t="s" s="2">
         <v>79</v>
@@ -9655,13 +9683,13 @@
         <v>79</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>246</v>
+        <v>292</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>79</v>
@@ -9673,50 +9701,56 @@
         <v>79</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>247</v>
+        <v>293</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>79</v>
       </c>
     </row>
-    <row r="68" hidden="true">
+    <row r="68">
       <c r="A68" t="s" s="2">
-        <v>418</v>
+        <v>424</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>408</v>
-      </c>
-      <c r="C68" s="2"/>
+        <v>416</v>
+      </c>
+      <c r="C68" t="s" s="2">
+        <v>425</v>
+      </c>
       <c r="D68" t="s" s="2">
         <v>79</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="G68" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H68" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="I68" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>103</v>
+        <v>241</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="N68" s="2"/>
-      <c r="O68" s="2"/>
+        <v>242</v>
+      </c>
+      <c r="N68" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="O68" t="s" s="2">
+        <v>244</v>
+      </c>
       <c r="P68" t="s" s="2">
         <v>79</v>
       </c>
@@ -9725,7 +9759,7 @@
         <v>79</v>
       </c>
       <c r="S68" t="s" s="2">
-        <v>79</v>
+        <v>426</v>
       </c>
       <c r="T68" t="s" s="2">
         <v>79</v>
@@ -9764,25 +9798,25 @@
         <v>79</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>105</v>
+        <v>246</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>79</v>
+        <v>247</v>
       </c>
       <c r="AM68" t="s" s="2">
         <v>79</v>
@@ -9790,21 +9824,21 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>419</v>
+        <v>427</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>107</v>
+        <v>79</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>79</v>
@@ -9816,17 +9850,15 @@
         <v>79</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>111</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="N69" s="2"/>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>79</v>
@@ -9863,31 +9895,31 @@
         <v>79</v>
       </c>
       <c r="AB69" t="s" s="2">
-        <v>112</v>
+        <v>79</v>
       </c>
       <c r="AC69" t="s" s="2">
-        <v>113</v>
+        <v>79</v>
       </c>
       <c r="AD69" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE69" t="s" s="2">
-        <v>114</v>
+        <v>79</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AI69" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>116</v>
+        <v>79</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>79</v>
@@ -9899,48 +9931,46 @@
         <v>79</v>
       </c>
     </row>
-    <row r="70">
+    <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>420</v>
+        <v>428</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>410</v>
+        <v>418</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>79</v>
+        <v>107</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H70" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="I70" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>129</v>
+        <v>108</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>256</v>
+        <v>109</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>257</v>
+        <v>110</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>258</v>
-      </c>
-      <c r="O70" t="s" s="2">
-        <v>259</v>
-      </c>
+        <v>111</v>
+      </c>
+      <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>79</v>
       </c>
@@ -9976,48 +10006,48 @@
         <v>79</v>
       </c>
       <c r="AB70" t="s" s="2">
-        <v>79</v>
+        <v>112</v>
       </c>
       <c r="AC70" t="s" s="2">
-        <v>79</v>
+        <v>113</v>
       </c>
       <c r="AD70" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE70" t="s" s="2">
-        <v>79</v>
+        <v>114</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>261</v>
+        <v>115</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>100</v>
+        <v>116</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>262</v>
+        <v>79</v>
       </c>
       <c r="AM70" t="s" s="2">
         <v>79</v>
       </c>
     </row>
-    <row r="71" hidden="true">
+    <row r="71">
       <c r="A71" t="s" s="2">
-        <v>421</v>
+        <v>429</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>411</v>
+        <v>419</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10025,13 +10055,13 @@
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="G71" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H71" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="I71" t="s" s="2">
         <v>79</v>
@@ -10040,18 +10070,20 @@
         <v>89</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>102</v>
+        <v>129</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>265</v>
+        <v>256</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>266</v>
+        <v>257</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="O71" s="2"/>
+        <v>258</v>
+      </c>
+      <c r="O71" t="s" s="2">
+        <v>259</v>
+      </c>
       <c r="P71" t="s" s="2">
         <v>79</v>
       </c>
@@ -10099,7 +10131,7 @@
         <v>79</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>77</v>
@@ -10117,18 +10149,18 @@
         <v>79</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>269</v>
+        <v>262</v>
       </c>
       <c r="AM71" t="s" s="2">
         <v>79</v>
       </c>
     </row>
-    <row r="72">
+    <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>422</v>
+        <v>430</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>412</v>
+        <v>420</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10136,13 +10168,13 @@
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="G72" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H72" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="I72" t="s" s="2">
         <v>79</v>
@@ -10151,18 +10183,18 @@
         <v>89</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>163</v>
+        <v>102</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="N72" s="2"/>
-      <c r="O72" t="s" s="2">
-        <v>274</v>
-      </c>
+        <v>266</v>
+      </c>
+      <c r="N72" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
         <v>79</v>
       </c>
@@ -10210,7 +10242,7 @@
         <v>79</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>77</v>
@@ -10228,7 +10260,7 @@
         <v>79</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>277</v>
+        <v>269</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>79</v>
@@ -10236,10 +10268,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>423</v>
+        <v>431</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>413</v>
+        <v>421</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10247,7 +10279,7 @@
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="G73" t="s" s="2">
         <v>88</v>
@@ -10262,17 +10294,17 @@
         <v>89</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>102</v>
+        <v>163</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>281</v>
+        <v>273</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" t="s" s="2">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>79</v>
@@ -10321,7 +10353,7 @@
         <v>79</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>77</v>
@@ -10339,18 +10371,18 @@
         <v>79</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>284</v>
+        <v>277</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>79</v>
       </c>
     </row>
-    <row r="74" hidden="true">
+    <row r="74">
       <c r="A74" t="s" s="2">
-        <v>424</v>
+        <v>432</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>414</v>
+        <v>422</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10364,7 +10396,7 @@
         <v>88</v>
       </c>
       <c r="H74" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="I74" t="s" s="2">
         <v>79</v>
@@ -10373,19 +10405,17 @@
         <v>89</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>287</v>
+        <v>102</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>288</v>
+        <v>280</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>290</v>
-      </c>
+        <v>281</v>
+      </c>
+      <c r="N74" s="2"/>
       <c r="O74" t="s" s="2">
-        <v>291</v>
+        <v>282</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>79</v>
@@ -10434,7 +10464,7 @@
         <v>79</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>292</v>
+        <v>283</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>77</v>
@@ -10452,7 +10482,7 @@
         <v>79</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>79</v>
@@ -10460,10 +10490,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>425</v>
+        <v>433</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10486,19 +10516,19 @@
         <v>89</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>102</v>
+        <v>287</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>299</v>
+        <v>291</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>79</v>
@@ -10547,7 +10577,7 @@
         <v>79</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>77</v>
@@ -10565,32 +10595,32 @@
         <v>79</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="AM75" t="s" s="2">
         <v>79</v>
       </c>
     </row>
-    <row r="76">
+    <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>426</v>
+        <v>434</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>426</v>
+        <v>434</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>427</v>
+        <v>79</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="G76" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H76" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="I76" t="s" s="2">
         <v>79</v>
@@ -10599,17 +10629,19 @@
         <v>89</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>428</v>
+        <v>102</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>429</v>
+        <v>296</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>430</v>
-      </c>
-      <c r="N76" s="2"/>
+        <v>297</v>
+      </c>
+      <c r="N76" t="s" s="2">
+        <v>298</v>
+      </c>
       <c r="O76" t="s" s="2">
-        <v>431</v>
+        <v>299</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>79</v>
@@ -10658,7 +10690,7 @@
         <v>79</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>426</v>
+        <v>300</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>77</v>
@@ -10673,16 +10705,16 @@
         <v>100</v>
       </c>
       <c r="AK76" t="s" s="2">
-        <v>432</v>
+        <v>79</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>433</v>
+        <v>301</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>434</v>
+        <v>79</v>
       </c>
     </row>
-    <row r="77" hidden="true">
+    <row r="77">
       <c r="A77" t="s" s="2">
         <v>435</v>
       </c>
@@ -10691,35 +10723,37 @@
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>79</v>
+        <v>436</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="G77" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H77" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="I77" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J77" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>102</v>
+        <v>437</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>103</v>
+        <v>438</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>104</v>
+        <v>439</v>
       </c>
       <c r="N77" s="2"/>
-      <c r="O77" s="2"/>
+      <c r="O77" t="s" s="2">
+        <v>440</v>
+      </c>
       <c r="P77" t="s" s="2">
         <v>79</v>
       </c>
@@ -10767,7 +10801,7 @@
         <v>79</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>105</v>
+        <v>435</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>77</v>
@@ -10779,35 +10813,35 @@
         <v>79</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="AK77" t="s" s="2">
-        <v>79</v>
+        <v>441</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>79</v>
+        <v>442</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>79</v>
+        <v>443</v>
       </c>
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>436</v>
+        <v>444</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>436</v>
+        <v>444</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
-        <v>107</v>
+        <v>79</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>79</v>
@@ -10819,17 +10853,15 @@
         <v>79</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="N78" t="s" s="2">
-        <v>111</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="N78" s="2"/>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
         <v>79</v>
@@ -10866,31 +10898,31 @@
         <v>79</v>
       </c>
       <c r="AB78" t="s" s="2">
-        <v>112</v>
+        <v>79</v>
       </c>
       <c r="AC78" t="s" s="2">
-        <v>113</v>
+        <v>79</v>
       </c>
       <c r="AD78" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE78" t="s" s="2">
-        <v>114</v>
+        <v>79</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AI78" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>116</v>
+        <v>79</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>79</v>
@@ -10902,44 +10934,44 @@
         <v>79</v>
       </c>
     </row>
-    <row r="79">
+    <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
-        <v>79</v>
+        <v>107</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H79" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="I79" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J79" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>346</v>
+        <v>109</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>347</v>
+        <v>110</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>348</v>
+        <v>111</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
@@ -10977,31 +11009,31 @@
         <v>79</v>
       </c>
       <c r="AB79" t="s" s="2">
-        <v>79</v>
+        <v>112</v>
       </c>
       <c r="AC79" t="s" s="2">
-        <v>79</v>
+        <v>113</v>
       </c>
       <c r="AD79" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE79" t="s" s="2">
-        <v>79</v>
+        <v>114</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>349</v>
+        <v>115</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH79" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AI79" t="s" s="2">
-        <v>350</v>
+        <v>79</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>100</v>
+        <v>116</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>79</v>
@@ -11013,12 +11045,12 @@
         <v>79</v>
       </c>
     </row>
-    <row r="80" hidden="true">
+    <row r="80">
       <c r="A80" t="s" s="2">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11032,7 +11064,7 @@
         <v>88</v>
       </c>
       <c r="H80" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="I80" t="s" s="2">
         <v>79</v>
@@ -11041,16 +11073,16 @@
         <v>89</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>129</v>
+        <v>102</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>354</v>
+        <v>348</v>
       </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
@@ -11076,13 +11108,13 @@
         <v>79</v>
       </c>
       <c r="X80" t="s" s="2">
-        <v>145</v>
+        <v>79</v>
       </c>
       <c r="Y80" t="s" s="2">
-        <v>355</v>
+        <v>79</v>
       </c>
       <c r="Z80" t="s" s="2">
-        <v>356</v>
+        <v>79</v>
       </c>
       <c r="AA80" t="s" s="2">
         <v>79</v>
@@ -11100,7 +11132,7 @@
         <v>79</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>357</v>
+        <v>349</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>77</v>
@@ -11109,7 +11141,7 @@
         <v>88</v>
       </c>
       <c r="AI80" t="s" s="2">
-        <v>79</v>
+        <v>350</v>
       </c>
       <c r="AJ80" t="s" s="2">
         <v>100</v>
@@ -11124,12 +11156,12 @@
         <v>79</v>
       </c>
     </row>
-    <row r="81">
+    <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>439</v>
+        <v>447</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>439</v>
+        <v>447</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11143,7 +11175,7 @@
         <v>88</v>
       </c>
       <c r="H81" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="I81" t="s" s="2">
         <v>79</v>
@@ -11152,16 +11184,16 @@
         <v>89</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>195</v>
+        <v>129</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>359</v>
+        <v>352</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>360</v>
+        <v>353</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>361</v>
+        <v>354</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -11187,13 +11219,13 @@
         <v>79</v>
       </c>
       <c r="X81" t="s" s="2">
-        <v>79</v>
+        <v>145</v>
       </c>
       <c r="Y81" t="s" s="2">
-        <v>79</v>
+        <v>355</v>
       </c>
       <c r="Z81" t="s" s="2">
-        <v>79</v>
+        <v>356</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>79</v>
@@ -11211,7 +11243,7 @@
         <v>79</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>77</v>
@@ -11235,12 +11267,12 @@
         <v>79</v>
       </c>
     </row>
-    <row r="82" hidden="true">
+    <row r="82">
       <c r="A82" t="s" s="2">
-        <v>440</v>
+        <v>448</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>440</v>
+        <v>448</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11254,7 +11286,7 @@
         <v>88</v>
       </c>
       <c r="H82" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="I82" t="s" s="2">
         <v>79</v>
@@ -11263,16 +11295,16 @@
         <v>89</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>102</v>
+        <v>195</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
@@ -11322,7 +11354,7 @@
         <v>79</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>77</v>
@@ -11346,16 +11378,16 @@
         <v>79</v>
       </c>
     </row>
-    <row r="83">
+    <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>441</v>
+        <v>449</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>441</v>
+        <v>449</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
-        <v>442</v>
+        <v>79</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
@@ -11365,7 +11397,7 @@
         <v>88</v>
       </c>
       <c r="H83" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="I83" t="s" s="2">
         <v>79</v>
@@ -11374,20 +11406,18 @@
         <v>89</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>443</v>
+        <v>102</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>444</v>
+        <v>364</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>445</v>
+        <v>365</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="O83" t="s" s="2">
-        <v>447</v>
-      </c>
+        <v>366</v>
+      </c>
+      <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
         <v>79</v>
       </c>
@@ -11435,7 +11465,7 @@
         <v>79</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>441</v>
+        <v>367</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>77</v>
@@ -11450,25 +11480,25 @@
         <v>100</v>
       </c>
       <c r="AK83" t="s" s="2">
-        <v>448</v>
+        <v>79</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>449</v>
+        <v>79</v>
       </c>
       <c r="AM83" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="s" s="2">
         <v>450</v>
       </c>
-    </row>
-    <row r="84" hidden="true">
-      <c r="A84" t="s" s="2">
-        <v>451</v>
-      </c>
       <c r="B84" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
-        <v>79</v>
+        <v>451</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
@@ -11478,25 +11508,29 @@
         <v>88</v>
       </c>
       <c r="H84" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="I84" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J84" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>102</v>
+        <v>452</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>103</v>
+        <v>453</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="N84" s="2"/>
-      <c r="O84" s="2"/>
+        <v>454</v>
+      </c>
+      <c r="N84" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="O84" t="s" s="2">
+        <v>456</v>
+      </c>
       <c r="P84" t="s" s="2">
         <v>79</v>
       </c>
@@ -11544,7 +11578,7 @@
         <v>79</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>105</v>
+        <v>450</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>77</v>
@@ -11556,35 +11590,35 @@
         <v>79</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="AK84" t="s" s="2">
-        <v>79</v>
+        <v>457</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>79</v>
+        <v>458</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>79</v>
+        <v>459</v>
       </c>
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>452</v>
+        <v>460</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>452</v>
+        <v>460</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
-        <v>107</v>
+        <v>79</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G85" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H85" t="s" s="2">
         <v>79</v>
@@ -11596,17 +11630,15 @@
         <v>79</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="N85" t="s" s="2">
-        <v>111</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="N85" s="2"/>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
         <v>79</v>
@@ -11643,31 +11675,31 @@
         <v>79</v>
       </c>
       <c r="AB85" t="s" s="2">
-        <v>112</v>
+        <v>79</v>
       </c>
       <c r="AC85" t="s" s="2">
-        <v>113</v>
+        <v>79</v>
       </c>
       <c r="AD85" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE85" t="s" s="2">
-        <v>114</v>
+        <v>79</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH85" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AI85" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>116</v>
+        <v>79</v>
       </c>
       <c r="AK85" t="s" s="2">
         <v>79</v>
@@ -11679,44 +11711,44 @@
         <v>79</v>
       </c>
     </row>
-    <row r="86">
+    <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>453</v>
+        <v>461</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>453</v>
+        <v>461</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
-        <v>79</v>
+        <v>107</v>
       </c>
       <c r="E86" s="2"/>
       <c r="F86" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G86" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H86" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="I86" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J86" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>346</v>
+        <v>109</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>347</v>
+        <v>110</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>348</v>
+        <v>111</v>
       </c>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
@@ -11754,31 +11786,31 @@
         <v>79</v>
       </c>
       <c r="AB86" t="s" s="2">
-        <v>79</v>
+        <v>112</v>
       </c>
       <c r="AC86" t="s" s="2">
-        <v>79</v>
+        <v>113</v>
       </c>
       <c r="AD86" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE86" t="s" s="2">
-        <v>79</v>
+        <v>114</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>349</v>
+        <v>115</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH86" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AI86" t="s" s="2">
-        <v>350</v>
+        <v>79</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>100</v>
+        <v>116</v>
       </c>
       <c r="AK86" t="s" s="2">
         <v>79</v>
@@ -11790,12 +11822,12 @@
         <v>79</v>
       </c>
     </row>
-    <row r="87" hidden="true">
+    <row r="87">
       <c r="A87" t="s" s="2">
-        <v>454</v>
+        <v>462</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>454</v>
+        <v>462</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -11809,7 +11841,7 @@
         <v>88</v>
       </c>
       <c r="H87" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="I87" t="s" s="2">
         <v>79</v>
@@ -11818,16 +11850,16 @@
         <v>89</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>129</v>
+        <v>102</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>354</v>
+        <v>348</v>
       </c>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
@@ -11853,13 +11885,13 @@
         <v>79</v>
       </c>
       <c r="X87" t="s" s="2">
-        <v>145</v>
+        <v>79</v>
       </c>
       <c r="Y87" t="s" s="2">
-        <v>355</v>
+        <v>79</v>
       </c>
       <c r="Z87" t="s" s="2">
-        <v>356</v>
+        <v>79</v>
       </c>
       <c r="AA87" t="s" s="2">
         <v>79</v>
@@ -11877,7 +11909,7 @@
         <v>79</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>357</v>
+        <v>349</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>77</v>
@@ -11886,7 +11918,7 @@
         <v>88</v>
       </c>
       <c r="AI87" t="s" s="2">
-        <v>79</v>
+        <v>350</v>
       </c>
       <c r="AJ87" t="s" s="2">
         <v>100</v>
@@ -11901,12 +11933,12 @@
         <v>79</v>
       </c>
     </row>
-    <row r="88">
+    <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>455</v>
+        <v>463</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>455</v>
+        <v>463</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -11920,7 +11952,7 @@
         <v>88</v>
       </c>
       <c r="H88" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="I88" t="s" s="2">
         <v>79</v>
@@ -11929,16 +11961,16 @@
         <v>89</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>195</v>
+        <v>129</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>359</v>
+        <v>352</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>360</v>
+        <v>353</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>361</v>
+        <v>354</v>
       </c>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
@@ -11964,13 +11996,13 @@
         <v>79</v>
       </c>
       <c r="X88" t="s" s="2">
-        <v>79</v>
+        <v>145</v>
       </c>
       <c r="Y88" t="s" s="2">
-        <v>79</v>
+        <v>355</v>
       </c>
       <c r="Z88" t="s" s="2">
-        <v>79</v>
+        <v>356</v>
       </c>
       <c r="AA88" t="s" s="2">
         <v>79</v>
@@ -11988,7 +12020,7 @@
         <v>79</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>77</v>
@@ -12012,12 +12044,12 @@
         <v>79</v>
       </c>
     </row>
-    <row r="89" hidden="true">
+    <row r="89">
       <c r="A89" t="s" s="2">
-        <v>456</v>
+        <v>464</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>456</v>
+        <v>464</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12031,7 +12063,7 @@
         <v>88</v>
       </c>
       <c r="H89" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="I89" t="s" s="2">
         <v>79</v>
@@ -12040,16 +12072,16 @@
         <v>89</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>102</v>
+        <v>195</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
@@ -12099,7 +12131,7 @@
         <v>79</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>77</v>
@@ -12123,26 +12155,26 @@
         <v>79</v>
       </c>
     </row>
-    <row r="90">
+    <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>457</v>
+        <v>465</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>457</v>
+        <v>465</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
-        <v>458</v>
+        <v>79</v>
       </c>
       <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="G90" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H90" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="I90" t="s" s="2">
         <v>79</v>
@@ -12151,20 +12183,18 @@
         <v>89</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>459</v>
+        <v>102</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>460</v>
+        <v>364</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>461</v>
+        <v>365</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>462</v>
-      </c>
-      <c r="O90" t="s" s="2">
-        <v>463</v>
-      </c>
+        <v>366</v>
+      </c>
+      <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
         <v>79</v>
       </c>
@@ -12212,7 +12242,7 @@
         <v>79</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>457</v>
+        <v>367</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>77</v>
@@ -12227,53 +12257,57 @@
         <v>100</v>
       </c>
       <c r="AK90" t="s" s="2">
-        <v>464</v>
+        <v>79</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>465</v>
+        <v>79</v>
       </c>
       <c r="AM90" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="s" s="2">
         <v>466</v>
       </c>
-    </row>
-    <row r="91" hidden="true">
-      <c r="A91" t="s" s="2">
-        <v>467</v>
-      </c>
       <c r="B91" t="s" s="2">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
-        <v>79</v>
+        <v>467</v>
       </c>
       <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="G91" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H91" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="I91" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J91" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>102</v>
+        <v>468</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>469</v>
-      </c>
-      <c r="N91" s="2"/>
-      <c r="O91" s="2"/>
+        <v>470</v>
+      </c>
+      <c r="N91" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="O91" t="s" s="2">
+        <v>472</v>
+      </c>
       <c r="P91" t="s" s="2">
         <v>79</v>
       </c>
@@ -12321,7 +12355,7 @@
         <v>79</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>105</v>
+        <v>466</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>77</v>
@@ -12333,24 +12367,24 @@
         <v>79</v>
       </c>
       <c r="AJ91" t="s" s="2">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="AK91" t="s" s="2">
-        <v>79</v>
+        <v>473</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>79</v>
+        <v>474</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>79</v>
+        <v>475</v>
       </c>
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>470</v>
+        <v>476</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>470</v>
+        <v>476</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -12361,7 +12395,7 @@
         <v>77</v>
       </c>
       <c r="G92" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H92" t="s" s="2">
         <v>79</v>
@@ -12373,13 +12407,13 @@
         <v>79</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>471</v>
+        <v>477</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>472</v>
+        <v>478</v>
       </c>
       <c r="N92" s="2"/>
       <c r="O92" s="2"/>
@@ -12418,29 +12452,31 @@
         <v>79</v>
       </c>
       <c r="AB92" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="AC92" s="2"/>
+        <v>79</v>
+      </c>
+      <c r="AC92" t="s" s="2">
+        <v>79</v>
+      </c>
       <c r="AD92" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE92" t="s" s="2">
-        <v>114</v>
+        <v>79</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH92" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AI92" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ92" t="s" s="2">
-        <v>116</v>
+        <v>79</v>
       </c>
       <c r="AK92" t="s" s="2">
         <v>79</v>
@@ -12452,16 +12488,14 @@
         <v>79</v>
       </c>
     </row>
-    <row r="93">
+    <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>473</v>
+        <v>479</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>470</v>
-      </c>
-      <c r="C93" t="s" s="2">
-        <v>474</v>
-      </c>
+        <v>479</v>
+      </c>
+      <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
         <v>79</v>
       </c>
@@ -12470,10 +12504,10 @@
         <v>77</v>
       </c>
       <c r="G93" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H93" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="I93" t="s" s="2">
         <v>79</v>
@@ -12482,13 +12516,13 @@
         <v>79</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>475</v>
+        <v>108</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" s="2"/>
@@ -12527,16 +12561,14 @@
         <v>79</v>
       </c>
       <c r="AB93" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC93" t="s" s="2">
-        <v>79</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="AC93" s="2"/>
       <c r="AD93" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE93" t="s" s="2">
-        <v>79</v>
+        <v>114</v>
       </c>
       <c r="AF93" t="s" s="2">
         <v>115</v>
@@ -12548,7 +12580,7 @@
         <v>78</v>
       </c>
       <c r="AI93" t="s" s="2">
-        <v>478</v>
+        <v>79</v>
       </c>
       <c r="AJ93" t="s" s="2">
         <v>116</v>
@@ -12563,14 +12595,16 @@
         <v>79</v>
       </c>
     </row>
-    <row r="94" hidden="true">
+    <row r="94">
       <c r="A94" t="s" s="2">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="B94" t="s" s="2">
         <v>479</v>
       </c>
-      <c r="C94" s="2"/>
+      <c r="C94" t="s" s="2">
+        <v>483</v>
+      </c>
       <c r="D94" t="s" s="2">
         <v>79</v>
       </c>
@@ -12582,7 +12616,7 @@
         <v>88</v>
       </c>
       <c r="H94" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="I94" t="s" s="2">
         <v>79</v>
@@ -12591,13 +12625,13 @@
         <v>79</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>459</v>
+        <v>484</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>481</v>
+        <v>486</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" s="2"/>
@@ -12648,19 +12682,19 @@
         <v>79</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>482</v>
+        <v>115</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH94" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AI94" t="s" s="2">
-        <v>79</v>
+        <v>487</v>
       </c>
       <c r="AJ94" t="s" s="2">
-        <v>79</v>
+        <v>116</v>
       </c>
       <c r="AK94" t="s" s="2">
         <v>79</v>
@@ -12672,48 +12706,44 @@
         <v>79</v>
       </c>
     </row>
-    <row r="95">
+    <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
-        <v>484</v>
+        <v>79</v>
       </c>
       <c r="E95" s="2"/>
       <c r="F95" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="G95" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H95" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="I95" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J95" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>123</v>
+        <v>468</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>486</v>
-      </c>
-      <c r="N95" t="s" s="2">
-        <v>487</v>
-      </c>
-      <c r="O95" t="s" s="2">
-        <v>488</v>
-      </c>
+        <v>490</v>
+      </c>
+      <c r="N95" s="2"/>
+      <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
         <v>79</v>
       </c>
@@ -12761,7 +12791,7 @@
         <v>79</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>483</v>
+        <v>491</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>77</v>
@@ -12773,35 +12803,35 @@
         <v>79</v>
       </c>
       <c r="AJ95" t="s" s="2">
-        <v>100</v>
+        <v>79</v>
       </c>
       <c r="AK95" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>489</v>
+        <v>79</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>490</v>
+        <v>79</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="E96" s="2"/>
       <c r="F96" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="G96" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H96" t="s" s="2">
         <v>89</v>
@@ -12813,7 +12843,7 @@
         <v>89</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>493</v>
+        <v>123</v>
       </c>
       <c r="L96" t="s" s="2">
         <v>494</v>
@@ -12874,13 +12904,13 @@
         <v>79</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH96" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AI96" t="s" s="2">
         <v>79</v>
@@ -12889,53 +12919,57 @@
         <v>100</v>
       </c>
       <c r="AK96" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL96" t="s" s="2">
         <v>498</v>
       </c>
-      <c r="AL96" t="s" s="2">
+      <c r="AM96" t="s" s="2">
         <v>499</v>
       </c>
-      <c r="AM96" t="s" s="2">
+    </row>
+    <row r="97">
+      <c r="A97" t="s" s="2">
         <v>500</v>
       </c>
-    </row>
-    <row r="97" hidden="true">
-      <c r="A97" t="s" s="2">
-        <v>501</v>
-      </c>
       <c r="B97" t="s" s="2">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
-        <v>79</v>
+        <v>501</v>
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G97" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H97" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="I97" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J97" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>102</v>
+        <v>502</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>103</v>
+        <v>503</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="N97" s="2"/>
-      <c r="O97" s="2"/>
+        <v>504</v>
+      </c>
+      <c r="N97" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="O97" t="s" s="2">
+        <v>506</v>
+      </c>
       <c r="P97" t="s" s="2">
         <v>79</v>
       </c>
@@ -12983,47 +13017,47 @@
         <v>79</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>105</v>
+        <v>500</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH97" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AI97" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ97" t="s" s="2">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="AK97" t="s" s="2">
-        <v>79</v>
+        <v>507</v>
       </c>
       <c r="AL97" t="s" s="2">
-        <v>79</v>
+        <v>508</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>79</v>
+        <v>509</v>
       </c>
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>502</v>
+        <v>510</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>502</v>
+        <v>510</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
-        <v>107</v>
+        <v>79</v>
       </c>
       <c r="E98" s="2"/>
       <c r="F98" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G98" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H98" t="s" s="2">
         <v>79</v>
@@ -13035,17 +13069,15 @@
         <v>79</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="N98" t="s" s="2">
-        <v>111</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="N98" s="2"/>
       <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
         <v>79</v>
@@ -13082,31 +13114,31 @@
         <v>79</v>
       </c>
       <c r="AB98" t="s" s="2">
-        <v>112</v>
+        <v>79</v>
       </c>
       <c r="AC98" t="s" s="2">
-        <v>113</v>
+        <v>79</v>
       </c>
       <c r="AD98" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE98" t="s" s="2">
-        <v>114</v>
+        <v>79</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH98" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AI98" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ98" t="s" s="2">
-        <v>116</v>
+        <v>79</v>
       </c>
       <c r="AK98" t="s" s="2">
         <v>79</v>
@@ -13118,44 +13150,44 @@
         <v>79</v>
       </c>
     </row>
-    <row r="99">
+    <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>503</v>
+        <v>511</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>503</v>
+        <v>511</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
-        <v>79</v>
+        <v>107</v>
       </c>
       <c r="E99" s="2"/>
       <c r="F99" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G99" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H99" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="I99" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J99" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>346</v>
+        <v>109</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>347</v>
+        <v>110</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>348</v>
+        <v>111</v>
       </c>
       <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
@@ -13193,31 +13225,31 @@
         <v>79</v>
       </c>
       <c r="AB99" t="s" s="2">
-        <v>79</v>
+        <v>112</v>
       </c>
       <c r="AC99" t="s" s="2">
-        <v>79</v>
+        <v>113</v>
       </c>
       <c r="AD99" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE99" t="s" s="2">
-        <v>79</v>
+        <v>114</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>349</v>
+        <v>115</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH99" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AI99" t="s" s="2">
-        <v>350</v>
+        <v>79</v>
       </c>
       <c r="AJ99" t="s" s="2">
-        <v>100</v>
+        <v>116</v>
       </c>
       <c r="AK99" t="s" s="2">
         <v>79</v>
@@ -13229,12 +13261,12 @@
         <v>79</v>
       </c>
     </row>
-    <row r="100" hidden="true">
+    <row r="100">
       <c r="A100" t="s" s="2">
-        <v>504</v>
+        <v>512</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>504</v>
+        <v>512</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -13248,7 +13280,7 @@
         <v>88</v>
       </c>
       <c r="H100" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="I100" t="s" s="2">
         <v>79</v>
@@ -13257,16 +13289,16 @@
         <v>89</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>129</v>
+        <v>102</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>354</v>
+        <v>348</v>
       </c>
       <c r="O100" s="2"/>
       <c r="P100" t="s" s="2">
@@ -13292,13 +13324,13 @@
         <v>79</v>
       </c>
       <c r="X100" t="s" s="2">
-        <v>145</v>
+        <v>79</v>
       </c>
       <c r="Y100" t="s" s="2">
-        <v>355</v>
+        <v>79</v>
       </c>
       <c r="Z100" t="s" s="2">
-        <v>356</v>
+        <v>79</v>
       </c>
       <c r="AA100" t="s" s="2">
         <v>79</v>
@@ -13316,7 +13348,7 @@
         <v>79</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>357</v>
+        <v>349</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>77</v>
@@ -13325,7 +13357,7 @@
         <v>88</v>
       </c>
       <c r="AI100" t="s" s="2">
-        <v>79</v>
+        <v>350</v>
       </c>
       <c r="AJ100" t="s" s="2">
         <v>100</v>
@@ -13340,12 +13372,12 @@
         <v>79</v>
       </c>
     </row>
-    <row r="101">
+    <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>505</v>
+        <v>513</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>505</v>
+        <v>513</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -13359,7 +13391,7 @@
         <v>88</v>
       </c>
       <c r="H101" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="I101" t="s" s="2">
         <v>79</v>
@@ -13368,16 +13400,16 @@
         <v>89</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>195</v>
+        <v>129</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>359</v>
+        <v>352</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>360</v>
+        <v>353</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>361</v>
+        <v>354</v>
       </c>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
@@ -13403,13 +13435,13 @@
         <v>79</v>
       </c>
       <c r="X101" t="s" s="2">
-        <v>79</v>
+        <v>145</v>
       </c>
       <c r="Y101" t="s" s="2">
-        <v>79</v>
+        <v>355</v>
       </c>
       <c r="Z101" t="s" s="2">
-        <v>79</v>
+        <v>356</v>
       </c>
       <c r="AA101" t="s" s="2">
         <v>79</v>
@@ -13427,7 +13459,7 @@
         <v>79</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>77</v>
@@ -13451,12 +13483,12 @@
         <v>79</v>
       </c>
     </row>
-    <row r="102" hidden="true">
+    <row r="102">
       <c r="A102" t="s" s="2">
-        <v>506</v>
+        <v>514</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>506</v>
+        <v>514</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -13470,7 +13502,7 @@
         <v>88</v>
       </c>
       <c r="H102" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="I102" t="s" s="2">
         <v>79</v>
@@ -13479,16 +13511,16 @@
         <v>89</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>102</v>
+        <v>195</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
@@ -13538,7 +13570,7 @@
         <v>79</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>77</v>
@@ -13564,21 +13596,21 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>507</v>
+        <v>515</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>507</v>
+        <v>515</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
-        <v>508</v>
+        <v>79</v>
       </c>
       <c r="E103" s="2"/>
       <c r="F103" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G103" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H103" t="s" s="2">
         <v>79</v>
@@ -13590,20 +13622,18 @@
         <v>89</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>493</v>
+        <v>102</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>509</v>
+        <v>364</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>510</v>
+        <v>365</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>511</v>
-      </c>
-      <c r="O103" t="s" s="2">
-        <v>497</v>
-      </c>
+        <v>366</v>
+      </c>
+      <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
         <v>79</v>
       </c>
@@ -13651,13 +13681,13 @@
         <v>79</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>507</v>
+        <v>367</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH103" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AI103" t="s" s="2">
         <v>79</v>
@@ -13666,25 +13696,25 @@
         <v>100</v>
       </c>
       <c r="AK103" t="s" s="2">
-        <v>498</v>
+        <v>79</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>512</v>
+        <v>79</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>500</v>
+        <v>79</v>
       </c>
     </row>
-    <row r="104">
+    <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
-        <v>79</v>
+        <v>517</v>
       </c>
       <c r="E104" s="2"/>
       <c r="F104" t="s" s="2">
@@ -13694,28 +13724,28 @@
         <v>78</v>
       </c>
       <c r="H104" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I104" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J104" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="I104" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J104" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="K104" t="s" s="2">
-        <v>514</v>
+        <v>502</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="O104" t="s" s="2">
-        <v>518</v>
+        <v>506</v>
       </c>
       <c r="P104" t="s" s="2">
         <v>79</v>
@@ -13764,7 +13794,7 @@
         <v>79</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>77</v>
@@ -13779,21 +13809,21 @@
         <v>100</v>
       </c>
       <c r="AK104" t="s" s="2">
-        <v>79</v>
+        <v>507</v>
       </c>
       <c r="AL104" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="AM104" t="s" s="2">
-        <v>79</v>
+        <v>509</v>
       </c>
     </row>
-    <row r="105" hidden="true">
+    <row r="105">
       <c r="A105" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -13804,10 +13834,10 @@
         <v>77</v>
       </c>
       <c r="G105" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H105" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="I105" t="s" s="2">
         <v>79</v>
@@ -13816,16 +13846,20 @@
         <v>79</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>102</v>
+        <v>523</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>103</v>
+        <v>524</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="N105" s="2"/>
-      <c r="O105" s="2"/>
+        <v>525</v>
+      </c>
+      <c r="N105" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="O105" t="s" s="2">
+        <v>527</v>
+      </c>
       <c r="P105" t="s" s="2">
         <v>79</v>
       </c>
@@ -13873,25 +13907,25 @@
         <v>79</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>105</v>
+        <v>522</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH105" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AI105" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ105" t="s" s="2">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="AK105" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL105" t="s" s="2">
-        <v>79</v>
+        <v>528</v>
       </c>
       <c r="AM105" t="s" s="2">
         <v>79</v>
@@ -13899,21 +13933,21 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>521</v>
+        <v>529</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>521</v>
+        <v>529</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
-        <v>107</v>
+        <v>79</v>
       </c>
       <c r="E106" s="2"/>
       <c r="F106" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G106" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H106" t="s" s="2">
         <v>79</v>
@@ -13925,17 +13959,15 @@
         <v>79</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="N106" t="s" s="2">
-        <v>111</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="N106" s="2"/>
       <c r="O106" s="2"/>
       <c r="P106" t="s" s="2">
         <v>79</v>
@@ -13972,31 +14004,31 @@
         <v>79</v>
       </c>
       <c r="AB106" t="s" s="2">
-        <v>112</v>
+        <v>79</v>
       </c>
       <c r="AC106" t="s" s="2">
-        <v>113</v>
+        <v>79</v>
       </c>
       <c r="AD106" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE106" t="s" s="2">
-        <v>114</v>
+        <v>79</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH106" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AI106" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ106" t="s" s="2">
-        <v>116</v>
+        <v>79</v>
       </c>
       <c r="AK106" t="s" s="2">
         <v>79</v>
@@ -14008,44 +14040,44 @@
         <v>79</v>
       </c>
     </row>
-    <row r="107">
+    <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>522</v>
+        <v>530</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>522</v>
+        <v>530</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
-        <v>79</v>
+        <v>107</v>
       </c>
       <c r="E107" s="2"/>
       <c r="F107" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G107" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H107" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="I107" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J107" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>346</v>
+        <v>109</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>347</v>
+        <v>110</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>348</v>
+        <v>111</v>
       </c>
       <c r="O107" s="2"/>
       <c r="P107" t="s" s="2">
@@ -14083,31 +14115,31 @@
         <v>79</v>
       </c>
       <c r="AB107" t="s" s="2">
-        <v>79</v>
+        <v>112</v>
       </c>
       <c r="AC107" t="s" s="2">
-        <v>79</v>
+        <v>113</v>
       </c>
       <c r="AD107" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE107" t="s" s="2">
-        <v>79</v>
+        <v>114</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>349</v>
+        <v>115</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH107" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AI107" t="s" s="2">
-        <v>350</v>
+        <v>79</v>
       </c>
       <c r="AJ107" t="s" s="2">
-        <v>100</v>
+        <v>116</v>
       </c>
       <c r="AK107" t="s" s="2">
         <v>79</v>
@@ -14119,12 +14151,12 @@
         <v>79</v>
       </c>
     </row>
-    <row r="108" hidden="true">
+    <row r="108">
       <c r="A108" t="s" s="2">
-        <v>523</v>
+        <v>531</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>523</v>
+        <v>531</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -14138,7 +14170,7 @@
         <v>88</v>
       </c>
       <c r="H108" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="I108" t="s" s="2">
         <v>79</v>
@@ -14147,16 +14179,16 @@
         <v>89</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>129</v>
+        <v>102</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>354</v>
+        <v>348</v>
       </c>
       <c r="O108" s="2"/>
       <c r="P108" t="s" s="2">
@@ -14182,13 +14214,13 @@
         <v>79</v>
       </c>
       <c r="X108" t="s" s="2">
-        <v>145</v>
+        <v>79</v>
       </c>
       <c r="Y108" t="s" s="2">
-        <v>355</v>
+        <v>79</v>
       </c>
       <c r="Z108" t="s" s="2">
-        <v>356</v>
+        <v>79</v>
       </c>
       <c r="AA108" t="s" s="2">
         <v>79</v>
@@ -14206,7 +14238,7 @@
         <v>79</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>357</v>
+        <v>349</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>77</v>
@@ -14215,7 +14247,7 @@
         <v>88</v>
       </c>
       <c r="AI108" t="s" s="2">
-        <v>79</v>
+        <v>350</v>
       </c>
       <c r="AJ108" t="s" s="2">
         <v>100</v>
@@ -14230,12 +14262,12 @@
         <v>79</v>
       </c>
     </row>
-    <row r="109">
+    <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>524</v>
+        <v>532</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>524</v>
+        <v>532</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -14249,7 +14281,7 @@
         <v>88</v>
       </c>
       <c r="H109" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="I109" t="s" s="2">
         <v>79</v>
@@ -14258,16 +14290,16 @@
         <v>89</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>195</v>
+        <v>129</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>359</v>
+        <v>352</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>360</v>
+        <v>353</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>361</v>
+        <v>354</v>
       </c>
       <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
@@ -14293,13 +14325,13 @@
         <v>79</v>
       </c>
       <c r="X109" t="s" s="2">
-        <v>79</v>
+        <v>145</v>
       </c>
       <c r="Y109" t="s" s="2">
-        <v>79</v>
+        <v>355</v>
       </c>
       <c r="Z109" t="s" s="2">
-        <v>79</v>
+        <v>356</v>
       </c>
       <c r="AA109" t="s" s="2">
         <v>79</v>
@@ -14317,7 +14349,7 @@
         <v>79</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>77</v>
@@ -14341,12 +14373,12 @@
         <v>79</v>
       </c>
     </row>
-    <row r="110" hidden="true">
+    <row r="110">
       <c r="A110" t="s" s="2">
-        <v>525</v>
+        <v>533</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>525</v>
+        <v>533</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -14360,7 +14392,7 @@
         <v>88</v>
       </c>
       <c r="H110" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="I110" t="s" s="2">
         <v>79</v>
@@ -14369,16 +14401,16 @@
         <v>89</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>102</v>
+        <v>195</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="O110" s="2"/>
       <c r="P110" t="s" s="2">
@@ -14428,7 +14460,7 @@
         <v>79</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>77</v>
@@ -14452,48 +14484,46 @@
         <v>79</v>
       </c>
     </row>
-    <row r="111">
+    <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>526</v>
+        <v>534</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>526</v>
+        <v>534</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
-        <v>527</v>
+        <v>79</v>
       </c>
       <c r="E111" s="2"/>
       <c r="F111" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="G111" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H111" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I111" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J111" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="I111" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J111" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="K111" t="s" s="2">
-        <v>528</v>
+        <v>102</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>529</v>
+        <v>364</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>530</v>
+        <v>365</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>531</v>
-      </c>
-      <c r="O111" t="s" s="2">
-        <v>532</v>
-      </c>
+        <v>366</v>
+      </c>
+      <c r="O111" s="2"/>
       <c r="P111" t="s" s="2">
         <v>79</v>
       </c>
@@ -14541,13 +14571,13 @@
         <v>79</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>526</v>
+        <v>367</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH111" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AI111" t="s" s="2">
         <v>79</v>
@@ -14559,32 +14589,32 @@
         <v>79</v>
       </c>
       <c r="AL111" t="s" s="2">
-        <v>533</v>
+        <v>79</v>
       </c>
       <c r="AM111" t="s" s="2">
         <v>79</v>
       </c>
     </row>
-    <row r="112" hidden="true">
+    <row r="112">
       <c r="A112" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
-        <v>79</v>
+        <v>536</v>
       </c>
       <c r="E112" s="2"/>
       <c r="F112" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="G112" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H112" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="I112" t="s" s="2">
         <v>79</v>
@@ -14593,16 +14623,20 @@
         <v>79</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>102</v>
+        <v>537</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>103</v>
+        <v>538</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="N112" s="2"/>
-      <c r="O112" s="2"/>
+        <v>539</v>
+      </c>
+      <c r="N112" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="O112" t="s" s="2">
+        <v>541</v>
+      </c>
       <c r="P112" t="s" s="2">
         <v>79</v>
       </c>
@@ -14650,25 +14684,25 @@
         <v>79</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>105</v>
+        <v>535</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH112" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AI112" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ112" t="s" s="2">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="AK112" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL112" t="s" s="2">
-        <v>79</v>
+        <v>542</v>
       </c>
       <c r="AM112" t="s" s="2">
         <v>79</v>
@@ -14676,21 +14710,21 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>535</v>
+        <v>543</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>535</v>
+        <v>543</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
-        <v>107</v>
+        <v>79</v>
       </c>
       <c r="E113" s="2"/>
       <c r="F113" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G113" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H113" t="s" s="2">
         <v>79</v>
@@ -14702,17 +14736,15 @@
         <v>79</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="N113" t="s" s="2">
-        <v>111</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="N113" s="2"/>
       <c r="O113" s="2"/>
       <c r="P113" t="s" s="2">
         <v>79</v>
@@ -14749,31 +14781,31 @@
         <v>79</v>
       </c>
       <c r="AB113" t="s" s="2">
-        <v>112</v>
+        <v>79</v>
       </c>
       <c r="AC113" t="s" s="2">
-        <v>113</v>
+        <v>79</v>
       </c>
       <c r="AD113" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE113" t="s" s="2">
-        <v>114</v>
+        <v>79</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH113" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AI113" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ113" t="s" s="2">
-        <v>116</v>
+        <v>79</v>
       </c>
       <c r="AK113" t="s" s="2">
         <v>79</v>
@@ -14785,44 +14817,44 @@
         <v>79</v>
       </c>
     </row>
-    <row r="114">
+    <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>536</v>
+        <v>544</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>536</v>
+        <v>544</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
-        <v>79</v>
+        <v>107</v>
       </c>
       <c r="E114" s="2"/>
       <c r="F114" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G114" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H114" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="I114" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J114" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>346</v>
+        <v>109</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>347</v>
+        <v>110</v>
       </c>
       <c r="N114" t="s" s="2">
-        <v>348</v>
+        <v>111</v>
       </c>
       <c r="O114" s="2"/>
       <c r="P114" t="s" s="2">
@@ -14860,31 +14892,31 @@
         <v>79</v>
       </c>
       <c r="AB114" t="s" s="2">
-        <v>79</v>
+        <v>112</v>
       </c>
       <c r="AC114" t="s" s="2">
-        <v>79</v>
+        <v>113</v>
       </c>
       <c r="AD114" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE114" t="s" s="2">
-        <v>79</v>
+        <v>114</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>349</v>
+        <v>115</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH114" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AI114" t="s" s="2">
-        <v>350</v>
+        <v>79</v>
       </c>
       <c r="AJ114" t="s" s="2">
-        <v>100</v>
+        <v>116</v>
       </c>
       <c r="AK114" t="s" s="2">
         <v>79</v>
@@ -14896,12 +14928,12 @@
         <v>79</v>
       </c>
     </row>
-    <row r="115" hidden="true">
+    <row r="115">
       <c r="A115" t="s" s="2">
-        <v>537</v>
+        <v>545</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>537</v>
+        <v>545</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -14915,7 +14947,7 @@
         <v>88</v>
       </c>
       <c r="H115" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="I115" t="s" s="2">
         <v>79</v>
@@ -14924,16 +14956,16 @@
         <v>89</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>129</v>
+        <v>102</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="N115" t="s" s="2">
-        <v>354</v>
+        <v>348</v>
       </c>
       <c r="O115" s="2"/>
       <c r="P115" t="s" s="2">
@@ -14959,13 +14991,13 @@
         <v>79</v>
       </c>
       <c r="X115" t="s" s="2">
-        <v>145</v>
+        <v>79</v>
       </c>
       <c r="Y115" t="s" s="2">
-        <v>355</v>
+        <v>79</v>
       </c>
       <c r="Z115" t="s" s="2">
-        <v>356</v>
+        <v>79</v>
       </c>
       <c r="AA115" t="s" s="2">
         <v>79</v>
@@ -14983,7 +15015,7 @@
         <v>79</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>357</v>
+        <v>349</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>77</v>
@@ -14992,7 +15024,7 @@
         <v>88</v>
       </c>
       <c r="AI115" t="s" s="2">
-        <v>79</v>
+        <v>350</v>
       </c>
       <c r="AJ115" t="s" s="2">
         <v>100</v>
@@ -15009,10 +15041,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>538</v>
+        <v>546</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>538</v>
+        <v>546</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -15035,16 +15067,16 @@
         <v>89</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>195</v>
+        <v>129</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>359</v>
+        <v>352</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>360</v>
+        <v>353</v>
       </c>
       <c r="N116" t="s" s="2">
-        <v>361</v>
+        <v>354</v>
       </c>
       <c r="O116" s="2"/>
       <c r="P116" t="s" s="2">
@@ -15070,13 +15102,13 @@
         <v>79</v>
       </c>
       <c r="X116" t="s" s="2">
-        <v>79</v>
+        <v>145</v>
       </c>
       <c r="Y116" t="s" s="2">
-        <v>79</v>
+        <v>355</v>
       </c>
       <c r="Z116" t="s" s="2">
-        <v>79</v>
+        <v>356</v>
       </c>
       <c r="AA116" t="s" s="2">
         <v>79</v>
@@ -15094,7 +15126,7 @@
         <v>79</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>77</v>
@@ -15120,10 +15152,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>539</v>
+        <v>547</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>539</v>
+        <v>547</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -15146,16 +15178,16 @@
         <v>89</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>102</v>
+        <v>195</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="N117" t="s" s="2">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="O117" s="2"/>
       <c r="P117" t="s" s="2">
@@ -15205,7 +15237,7 @@
         <v>79</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>77</v>
@@ -15231,10 +15263,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>540</v>
+        <v>548</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>540</v>
+        <v>548</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -15245,7 +15277,7 @@
         <v>77</v>
       </c>
       <c r="G118" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H118" t="s" s="2">
         <v>79</v>
@@ -15254,19 +15286,19 @@
         <v>79</v>
       </c>
       <c r="J118" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>541</v>
+        <v>102</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>542</v>
+        <v>364</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>543</v>
+        <v>365</v>
       </c>
       <c r="N118" t="s" s="2">
-        <v>544</v>
+        <v>366</v>
       </c>
       <c r="O118" s="2"/>
       <c r="P118" t="s" s="2">
@@ -15316,13 +15348,13 @@
         <v>79</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>540</v>
+        <v>367</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH118" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AI118" t="s" s="2">
         <v>79</v>
@@ -15342,14 +15374,14 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
-        <v>546</v>
+        <v>79</v>
       </c>
       <c r="E119" s="2"/>
       <c r="F119" t="s" s="2">
@@ -15365,21 +15397,21 @@
         <v>79</v>
       </c>
       <c r="J119" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>549</v>
-      </c>
-      <c r="N119" s="2"/>
-      <c r="O119" t="s" s="2">
-        <v>550</v>
-      </c>
+        <v>552</v>
+      </c>
+      <c r="N119" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="O119" s="2"/>
       <c r="P119" t="s" s="2">
         <v>79</v>
       </c>
@@ -15427,7 +15459,7 @@
         <v>79</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>77</v>
@@ -15445,7 +15477,7 @@
         <v>79</v>
       </c>
       <c r="AL119" t="s" s="2">
-        <v>551</v>
+        <v>79</v>
       </c>
       <c r="AM119" t="s" s="2">
         <v>79</v>
@@ -15453,21 +15485,21 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
-        <v>79</v>
+        <v>555</v>
       </c>
       <c r="E120" s="2"/>
       <c r="F120" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G120" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H120" t="s" s="2">
         <v>79</v>
@@ -15476,19 +15508,21 @@
         <v>79</v>
       </c>
       <c r="J120" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>102</v>
+        <v>556</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>103</v>
+        <v>557</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>104</v>
+        <v>558</v>
       </c>
       <c r="N120" s="2"/>
-      <c r="O120" s="2"/>
+      <c r="O120" t="s" s="2">
+        <v>559</v>
+      </c>
       <c r="P120" t="s" s="2">
         <v>79</v>
       </c>
@@ -15536,25 +15570,25 @@
         <v>79</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>105</v>
+        <v>554</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH120" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AI120" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ120" t="s" s="2">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="AK120" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL120" t="s" s="2">
-        <v>79</v>
+        <v>560</v>
       </c>
       <c r="AM120" t="s" s="2">
         <v>79</v>
@@ -15562,21 +15596,21 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>553</v>
+        <v>561</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>553</v>
+        <v>561</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
-        <v>107</v>
+        <v>79</v>
       </c>
       <c r="E121" s="2"/>
       <c r="F121" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G121" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H121" t="s" s="2">
         <v>79</v>
@@ -15588,17 +15622,15 @@
         <v>79</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="N121" t="s" s="2">
-        <v>111</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="N121" s="2"/>
       <c r="O121" s="2"/>
       <c r="P121" t="s" s="2">
         <v>79</v>
@@ -15647,19 +15679,19 @@
         <v>79</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH121" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AI121" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ121" t="s" s="2">
-        <v>116</v>
+        <v>79</v>
       </c>
       <c r="AK121" t="s" s="2">
         <v>79</v>
@@ -15673,14 +15705,14 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>554</v>
+        <v>562</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>554</v>
+        <v>562</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
-        <v>555</v>
+        <v>107</v>
       </c>
       <c r="E122" s="2"/>
       <c r="F122" t="s" s="2">
@@ -15693,26 +15725,24 @@
         <v>79</v>
       </c>
       <c r="I122" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="J122" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="K122" t="s" s="2">
         <v>108</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>556</v>
+        <v>109</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>557</v>
+        <v>110</v>
       </c>
       <c r="N122" t="s" s="2">
         <v>111</v>
       </c>
-      <c r="O122" t="s" s="2">
-        <v>191</v>
-      </c>
+      <c r="O122" s="2"/>
       <c r="P122" t="s" s="2">
         <v>79</v>
       </c>
@@ -15760,7 +15790,7 @@
         <v>79</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>558</v>
+        <v>115</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>77</v>
@@ -15786,45 +15816,45 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>559</v>
+        <v>563</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>559</v>
+        <v>563</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
-        <v>79</v>
+        <v>564</v>
       </c>
       <c r="E123" s="2"/>
       <c r="F123" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G123" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H123" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I123" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="J123" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>560</v>
+        <v>565</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>561</v>
+        <v>566</v>
       </c>
       <c r="N123" t="s" s="2">
-        <v>562</v>
+        <v>111</v>
       </c>
       <c r="O123" t="s" s="2">
-        <v>563</v>
+        <v>191</v>
       </c>
       <c r="P123" t="s" s="2">
         <v>79</v>
@@ -15873,19 +15903,19 @@
         <v>79</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>559</v>
+        <v>567</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH123" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AI123" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ123" t="s" s="2">
-        <v>100</v>
+        <v>116</v>
       </c>
       <c r="AK123" t="s" s="2">
         <v>79</v>
@@ -15899,10 +15929,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -15910,7 +15940,7 @@
       </c>
       <c r="E124" s="2"/>
       <c r="F124" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="G124" t="s" s="2">
         <v>88</v>
@@ -15922,19 +15952,23 @@
         <v>79</v>
       </c>
       <c r="J124" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>565</v>
+        <v>102</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>567</v>
-      </c>
-      <c r="N124" s="2"/>
-      <c r="O124" s="2"/>
+        <v>570</v>
+      </c>
+      <c r="N124" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="O124" t="s" s="2">
+        <v>572</v>
+      </c>
       <c r="P124" t="s" s="2">
         <v>79</v>
       </c>
@@ -15982,10 +16016,10 @@
         <v>79</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="AG124" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="AH124" t="s" s="2">
         <v>88</v>
@@ -16006,46 +16040,44 @@
         <v>79</v>
       </c>
     </row>
-    <row r="125">
+    <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>568</v>
+        <v>573</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>568</v>
+        <v>573</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
-        <v>569</v>
+        <v>79</v>
       </c>
       <c r="E125" s="2"/>
       <c r="F125" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="G125" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H125" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I125" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J125" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="I125" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J125" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="K125" t="s" s="2">
-        <v>102</v>
+        <v>574</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>570</v>
+        <v>575</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>571</v>
+        <v>576</v>
       </c>
       <c r="N125" s="2"/>
-      <c r="O125" t="s" s="2">
-        <v>572</v>
-      </c>
+      <c r="O125" s="2"/>
       <c r="P125" t="s" s="2">
         <v>79</v>
       </c>
@@ -16093,10 +16125,10 @@
         <v>79</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>568</v>
+        <v>573</v>
       </c>
       <c r="AG125" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="AH125" t="s" s="2">
         <v>88</v>
@@ -16111,32 +16143,32 @@
         <v>79</v>
       </c>
       <c r="AL125" t="s" s="2">
-        <v>573</v>
+        <v>79</v>
       </c>
       <c r="AM125" t="s" s="2">
         <v>79</v>
       </c>
     </row>
-    <row r="126" hidden="true">
+    <row r="126">
       <c r="A126" t="s" s="2">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
-        <v>79</v>
+        <v>578</v>
       </c>
       <c r="E126" s="2"/>
       <c r="F126" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G126" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H126" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="I126" t="s" s="2">
         <v>79</v>
@@ -16145,16 +16177,18 @@
         <v>79</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>225</v>
+        <v>102</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>575</v>
+        <v>579</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>576</v>
+        <v>580</v>
       </c>
       <c r="N126" s="2"/>
-      <c r="O126" s="2"/>
+      <c r="O126" t="s" s="2">
+        <v>581</v>
+      </c>
       <c r="P126" t="s" s="2">
         <v>79</v>
       </c>
@@ -16178,37 +16212,37 @@
         <v>79</v>
       </c>
       <c r="X126" t="s" s="2">
-        <v>153</v>
+        <v>79</v>
       </c>
       <c r="Y126" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z126" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA126" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB126" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC126" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD126" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE126" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF126" t="s" s="2">
         <v>577</v>
       </c>
-      <c r="Z126" t="s" s="2">
-        <v>578</v>
-      </c>
-      <c r="AA126" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB126" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC126" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD126" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE126" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF126" t="s" s="2">
-        <v>574</v>
-      </c>
       <c r="AG126" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH126" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AI126" t="s" s="2">
         <v>79</v>
@@ -16220,7 +16254,7 @@
         <v>79</v>
       </c>
       <c r="AL126" t="s" s="2">
-        <v>573</v>
+        <v>582</v>
       </c>
       <c r="AM126" t="s" s="2">
         <v>79</v>
@@ -16228,10 +16262,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>579</v>
+        <v>583</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>579</v>
+        <v>583</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -16254,20 +16288,16 @@
         <v>79</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>580</v>
+        <v>225</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>582</v>
-      </c>
-      <c r="N127" t="s" s="2">
-        <v>583</v>
-      </c>
-      <c r="O127" t="s" s="2">
-        <v>584</v>
-      </c>
+        <v>585</v>
+      </c>
+      <c r="N127" s="2"/>
+      <c r="O127" s="2"/>
       <c r="P127" t="s" s="2">
         <v>79</v>
       </c>
@@ -16291,13 +16321,13 @@
         <v>79</v>
       </c>
       <c r="X127" t="s" s="2">
-        <v>79</v>
+        <v>153</v>
       </c>
       <c r="Y127" t="s" s="2">
-        <v>79</v>
+        <v>586</v>
       </c>
       <c r="Z127" t="s" s="2">
-        <v>79</v>
+        <v>587</v>
       </c>
       <c r="AA127" t="s" s="2">
         <v>79</v>
@@ -16315,7 +16345,7 @@
         <v>79</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>579</v>
+        <v>583</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>77</v>
@@ -16333,14 +16363,127 @@
         <v>79</v>
       </c>
       <c r="AL127" t="s" s="2">
-        <v>573</v>
+        <v>582</v>
       </c>
       <c r="AM127" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="128" hidden="true">
+      <c r="A128" t="s" s="2">
+        <v>588</v>
+      </c>
+      <c r="B128" t="s" s="2">
+        <v>588</v>
+      </c>
+      <c r="C128" s="2"/>
+      <c r="D128" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E128" s="2"/>
+      <c r="F128" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G128" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H128" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I128" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J128" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K128" t="s" s="2">
+        <v>589</v>
+      </c>
+      <c r="L128" t="s" s="2">
+        <v>590</v>
+      </c>
+      <c r="M128" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="N128" t="s" s="2">
+        <v>592</v>
+      </c>
+      <c r="O128" t="s" s="2">
+        <v>593</v>
+      </c>
+      <c r="P128" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Q128" s="2"/>
+      <c r="R128" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="S128" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="T128" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="U128" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="V128" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="W128" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="X128" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Y128" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="Z128" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA128" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB128" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC128" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD128" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE128" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF128" t="s" s="2">
+        <v>588</v>
+      </c>
+      <c r="AG128" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH128" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI128" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AJ128" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK128" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL128" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="AM128" t="s" s="2">
         <v>79</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AM127">
+  <autoFilter ref="A1:AM128">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -16350,7 +16493,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI126">
+  <conditionalFormatting sqref="A2:AI127">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/branches/master/StructureDefinition-mii-pr-labor-laborbefund.xlsx
+++ b/branches/master/StructureDefinition-mii-pr-labor-laborbefund.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T15:00:33+00:00</t>
+    <t>2026-09-02T15:34:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-mii-pr-labor-laborbefund.xlsx
+++ b/branches/master/StructureDefinition-mii-pr-labor-laborbefund.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T15:34:02+00:00</t>
+    <t>2026-09-02T17:45:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-mii-pr-labor-laborbefund.xlsx
+++ b/branches/master/StructureDefinition-mii-pr-labor-laborbefund.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T17:45:23+00:00</t>
+    <t>2026-09-02T17:52:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-mii-pr-labor-laborbefund.xlsx
+++ b/branches/master/StructureDefinition-mii-pr-labor-laborbefund.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot.rc1</t>
+    <t>2027.0.0-ballot.rc2</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T17:52:09+00:00</t>
+    <t>2026-09-02T18:06:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1210,55 +1210,51 @@
     <t>http://hl7.org/fhir/ValueSet/diagnostic-service-sections|4.0.1</t>
   </si>
   <si>
+    <t xml:space="preserve">pattern:coding}
+</t>
+  </si>
+  <si>
+    <t>OBR-24</t>
+  </si>
+  <si>
+    <t>FiveWs.class</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.category:laborbefund</t>
+  </si>
+  <si>
+    <t>laborbefund</t>
+  </si>
+  <si>
+    <t>Laborbefund-Kategorie</t>
+  </si>
+  <si>
+    <t>Die verpflichtende Kategorie des Laborbefunds. Weitere Kategorien, etwa der Laborbereich, sind als zusaetzliche category-Eintraege zulaessig.</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.category:laborbefund.id</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.category.id</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.category:laborbefund.extension</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.category.extension</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.category:laborbefund.coding</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.category.coding</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
     <t xml:space="preserve">pattern:$this}
 </t>
-  </si>
-  <si>
-    <t>OBR-24</t>
-  </si>
-  <si>
-    <t>FiveWs.class</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.category:laborbefund</t>
-  </si>
-  <si>
-    <t>laborbefund</t>
-  </si>
-  <si>
-    <t>Laborbefund-Kategorie</t>
-  </si>
-  <si>
-    <t>Die verpflichtende Kategorie des Laborbefunds. Weitere Kategorien, etwa der Laborbereich, sind als zusaetzliche category-Eintraege zulaessig.</t>
-  </si>
-  <si>
-    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
-  &lt;coding&gt;
-    &lt;system value="http://loinc.org"/&gt;
-    &lt;code value="26436-6"/&gt;
-  &lt;/coding&gt;
-&lt;/valueCodeableConcept&gt;</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.category:laborbefund.id</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.category.id</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.category:laborbefund.extension</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.category.extension</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.category:laborbefund.coding</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.category.coding</t>
-  </si>
-  <si>
-    <t>2</t>
   </si>
   <si>
     <t>DiagnosticReport.category:laborbefund.coding:loinc-lab</t>
@@ -7751,7 +7747,7 @@
         <v>79</v>
       </c>
       <c r="S50" t="s" s="2">
-        <v>390</v>
+        <v>79</v>
       </c>
       <c r="T50" t="s" s="2">
         <v>79</v>
@@ -7816,10 +7812,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="B51" t="s" s="2">
         <v>391</v>
-      </c>
-      <c r="B51" t="s" s="2">
-        <v>392</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7925,10 +7921,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="B52" t="s" s="2">
         <v>393</v>
-      </c>
-      <c r="B52" t="s" s="2">
-        <v>394</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8036,10 +8032,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="B53" t="s" s="2">
         <v>395</v>
-      </c>
-      <c r="B53" t="s" s="2">
-        <v>396</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8047,7 +8043,7 @@
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="G53" t="s" s="2">
         <v>78</v>
@@ -8111,7 +8107,7 @@
         <v>79</v>
       </c>
       <c r="AB53" t="s" s="2">
-        <v>383</v>
+        <v>397</v>
       </c>
       <c r="AC53" s="2"/>
       <c r="AD53" t="s" s="2">
@@ -8150,7 +8146,7 @@
         <v>398</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C54" t="s" s="2">
         <v>399</v>
@@ -8265,7 +8261,7 @@
         <v>401</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C55" t="s" s="2">
         <v>402</v>
@@ -8894,7 +8890,7 @@
         <v>79</v>
       </c>
       <c r="AB60" t="s" s="2">
-        <v>383</v>
+        <v>397</v>
       </c>
       <c r="AC60" s="2"/>
       <c r="AD60" t="s" s="2">

--- a/branches/master/StructureDefinition-mii-pr-labor-laborbefund.xlsx
+++ b/branches/master/StructureDefinition-mii-pr-labor-laborbefund.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AM$128</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AM$122</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4533" uniqueCount="594">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4319" uniqueCount="579">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot.rc2</t>
+    <t>2027.0.0-ballot.rc3</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T18:06:21+00:00</t>
+    <t>2026-09-02T20:13:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1210,81 +1210,34 @@
     <t>http://hl7.org/fhir/ValueSet/diagnostic-service-sections|4.0.1</t>
   </si>
   <si>
-    <t xml:space="preserve">pattern:coding}
-</t>
-  </si>
-  <si>
-    <t>OBR-24</t>
-  </si>
-  <si>
-    <t>FiveWs.class</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.category:laborbefund</t>
-  </si>
-  <si>
-    <t>laborbefund</t>
-  </si>
-  <si>
-    <t>Laborbefund-Kategorie</t>
-  </si>
-  <si>
-    <t>Die verpflichtende Kategorie des Laborbefunds. Weitere Kategorien, etwa der Laborbereich, sind als zusaetzliche category-Eintraege zulaessig.</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.category:laborbefund.id</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.category.id</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.category:laborbefund.extension</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.category.extension</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.category:laborbefund.coding</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.category.coding</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
     <t xml:space="preserve">pattern:$this}
 </t>
   </si>
   <si>
-    <t>DiagnosticReport.category:laborbefund.coding:loinc-lab</t>
-  </si>
-  <si>
-    <t>loinc-lab</t>
-  </si>
-  <si>
-    <t>&lt;valueCoding xmlns="http://hl7.org/fhir"&gt;
-  &lt;system value="http://loinc.org"/&gt;
-  &lt;code value="26436-6"/&gt;
-&lt;/valueCoding&gt;</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.category:laborbefund.coding:diagnostic-service-sections</t>
-  </si>
-  <si>
-    <t>diagnostic-service-sections</t>
-  </si>
-  <si>
-    <t>&lt;valueCoding xmlns="http://hl7.org/fhir"&gt;
-  &lt;system value="http://terminology.hl7.org/CodeSystem/v2-0074"/&gt;
-  &lt;code value="LAB"/&gt;
-&lt;/valueCoding&gt;</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.category:laborbefund.text</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.category.text</t>
+    <t>OBR-24</t>
+  </si>
+  <si>
+    <t>FiveWs.class</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.category:v2-lab</t>
+  </si>
+  <si>
+    <t>v2-lab</t>
+  </si>
+  <si>
+    <t>Labor-Kategorie</t>
+  </si>
+  <si>
+    <t>Die verpflichtende Kategorie des Laborbefunds. Weitere Codings im selben Eintrag und weitere category-Eintraege sind zulaessig.</t>
+  </si>
+  <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="http://terminology.hl7.org/CodeSystem/v2-0074"/&gt;
+    &lt;code value="LAB"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
     <t>DiagnosticReport.code</t>
@@ -2199,10 +2152,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AM128"/>
+  <dimension ref="A1:AM122"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="59.58203125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="56.33984375" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="42.53515625" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="24.5234375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="53.34375" customWidth="true" bestFit="true" hidden="true"/>
@@ -7747,7 +7700,7 @@
         <v>79</v>
       </c>
       <c r="S50" t="s" s="2">
-        <v>79</v>
+        <v>390</v>
       </c>
       <c r="T50" t="s" s="2">
         <v>79</v>
@@ -7810,41 +7763,41 @@
         <v>385</v>
       </c>
     </row>
-    <row r="51" hidden="true">
+    <row r="51">
       <c r="A51" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B51" t="s" s="2">
         <v>391</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>79</v>
+        <v>392</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="G51" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H51" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="I51" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>102</v>
+        <v>225</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>103</v>
+        <v>63</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>104</v>
+        <v>393</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7871,13 +7824,13 @@
         <v>79</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>79</v>
+        <v>167</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>79</v>
+        <v>394</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>79</v>
+        <v>395</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>79</v>
@@ -7895,10 +7848,10 @@
         <v>79</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>105</v>
+        <v>391</v>
       </c>
       <c r="AG51" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="AH51" t="s" s="2">
         <v>88</v>
@@ -7907,35 +7860,35 @@
         <v>79</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>79</v>
+        <v>396</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>79</v>
+        <v>397</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>79</v>
+        <v>398</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>392</v>
+        <v>399</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>393</v>
+        <v>399</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>107</v>
+        <v>79</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>79</v>
@@ -7947,17 +7900,15 @@
         <v>79</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>111</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="N52" s="2"/>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>79</v>
@@ -7994,31 +7945,31 @@
         <v>79</v>
       </c>
       <c r="AB52" t="s" s="2">
-        <v>112</v>
+        <v>79</v>
       </c>
       <c r="AC52" t="s" s="2">
-        <v>113</v>
+        <v>79</v>
       </c>
       <c r="AD52" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE52" t="s" s="2">
-        <v>114</v>
+        <v>79</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>116</v>
+        <v>79</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>79</v>
@@ -8032,18 +7983,18 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>394</v>
+        <v>400</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>79</v>
+        <v>107</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
-        <v>396</v>
+        <v>77</v>
       </c>
       <c r="G53" t="s" s="2">
         <v>78</v>
@@ -8055,23 +8006,21 @@
         <v>79</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>141</v>
+        <v>108</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>241</v>
+        <v>109</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>242</v>
+        <v>110</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>243</v>
-      </c>
-      <c r="O53" t="s" s="2">
-        <v>244</v>
-      </c>
+        <v>111</v>
+      </c>
+      <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>79</v>
       </c>
@@ -8107,9 +8056,11 @@
         <v>79</v>
       </c>
       <c r="AB53" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="AC53" s="2"/>
+        <v>112</v>
+      </c>
+      <c r="AC53" t="s" s="2">
+        <v>113</v>
+      </c>
       <c r="AD53" t="s" s="2">
         <v>79</v>
       </c>
@@ -8117,7 +8068,7 @@
         <v>114</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>246</v>
+        <v>115</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>77</v>
@@ -8129,28 +8080,26 @@
         <v>79</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>100</v>
+        <v>116</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>247</v>
+        <v>79</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>79</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>395</v>
-      </c>
-      <c r="C54" t="s" s="2">
-        <v>399</v>
-      </c>
+        <v>401</v>
+      </c>
+      <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
         <v>79</v>
       </c>
@@ -8159,7 +8108,7 @@
         <v>88</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>89</v>
@@ -8193,7 +8142,7 @@
         <v>79</v>
       </c>
       <c r="S54" t="s" s="2">
-        <v>400</v>
+        <v>79</v>
       </c>
       <c r="T54" t="s" s="2">
         <v>79</v>
@@ -8220,16 +8169,14 @@
         <v>79</v>
       </c>
       <c r="AB54" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC54" t="s" s="2">
-        <v>79</v>
-      </c>
+        <v>383</v>
+      </c>
+      <c r="AC54" s="2"/>
       <c r="AD54" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE54" t="s" s="2">
-        <v>79</v>
+        <v>114</v>
       </c>
       <c r="AF54" t="s" s="2">
         <v>246</v>
@@ -8256,50 +8203,44 @@
         <v>79</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>395</v>
-      </c>
-      <c r="C55" t="s" s="2">
         <v>402</v>
       </c>
+      <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
         <v>79</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="G55" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H55" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="I55" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>241</v>
+        <v>103</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>243</v>
-      </c>
-      <c r="O55" t="s" s="2">
-        <v>244</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="N55" s="2"/>
+      <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>79</v>
       </c>
@@ -8308,7 +8249,7 @@
         <v>79</v>
       </c>
       <c r="S55" t="s" s="2">
-        <v>403</v>
+        <v>79</v>
       </c>
       <c r="T55" t="s" s="2">
         <v>79</v>
@@ -8347,25 +8288,25 @@
         <v>79</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>246</v>
+        <v>105</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>100</v>
+        <v>79</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>247</v>
+        <v>79</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>79</v>
@@ -8373,21 +8314,21 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>79</v>
+        <v>107</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>79</v>
@@ -8396,23 +8337,21 @@
         <v>79</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>296</v>
+        <v>109</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>297</v>
+        <v>110</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>298</v>
-      </c>
-      <c r="O56" t="s" s="2">
-        <v>299</v>
-      </c>
+        <v>111</v>
+      </c>
+      <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>79</v>
       </c>
@@ -8448,37 +8387,37 @@
         <v>79</v>
       </c>
       <c r="AB56" t="s" s="2">
-        <v>79</v>
+        <v>112</v>
       </c>
       <c r="AC56" t="s" s="2">
-        <v>79</v>
+        <v>113</v>
       </c>
       <c r="AD56" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE56" t="s" s="2">
-        <v>79</v>
+        <v>114</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>300</v>
+        <v>115</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>100</v>
+        <v>116</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>301</v>
+        <v>79</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>79</v>
@@ -8486,14 +8425,14 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>407</v>
+        <v>79</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
@@ -8512,16 +8451,20 @@
         <v>89</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>225</v>
+        <v>129</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>63</v>
+        <v>256</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>408</v>
-      </c>
-      <c r="N57" s="2"/>
-      <c r="O57" s="2"/>
+        <v>257</v>
+      </c>
+      <c r="N57" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="O57" t="s" s="2">
+        <v>259</v>
+      </c>
       <c r="P57" t="s" s="2">
         <v>79</v>
       </c>
@@ -8545,13 +8488,13 @@
         <v>79</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>167</v>
+        <v>79</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>409</v>
+        <v>79</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>410</v>
+        <v>79</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>79</v>
@@ -8569,10 +8512,10 @@
         <v>79</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>406</v>
+        <v>261</v>
       </c>
       <c r="AG57" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="AH57" t="s" s="2">
         <v>88</v>
@@ -8584,21 +8527,21 @@
         <v>100</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>411</v>
+        <v>79</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>412</v>
+        <v>262</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>413</v>
+        <v>79</v>
       </c>
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>414</v>
+        <v>405</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>414</v>
+        <v>405</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8618,18 +8561,20 @@
         <v>79</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="K58" t="s" s="2">
         <v>102</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>103</v>
+        <v>265</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="N58" s="2"/>
+        <v>266</v>
+      </c>
+      <c r="N58" t="s" s="2">
+        <v>267</v>
+      </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>79</v>
@@ -8678,7 +8623,7 @@
         <v>79</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>105</v>
+        <v>268</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>77</v>
@@ -8690,58 +8635,58 @@
         <v>79</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>79</v>
+        <v>269</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>79</v>
       </c>
     </row>
-    <row r="59" hidden="true">
+    <row r="59">
       <c r="A59" t="s" s="2">
-        <v>415</v>
+        <v>406</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>415</v>
+        <v>406</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>107</v>
+        <v>79</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H59" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="I59" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>108</v>
+        <v>163</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>109</v>
+        <v>272</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="O59" s="2"/>
+        <v>273</v>
+      </c>
+      <c r="N59" s="2"/>
+      <c r="O59" t="s" s="2">
+        <v>274</v>
+      </c>
       <c r="P59" t="s" s="2">
         <v>79</v>
       </c>
@@ -8777,48 +8722,48 @@
         <v>79</v>
       </c>
       <c r="AB59" t="s" s="2">
-        <v>112</v>
+        <v>79</v>
       </c>
       <c r="AC59" t="s" s="2">
-        <v>113</v>
+        <v>79</v>
       </c>
       <c r="AD59" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE59" t="s" s="2">
-        <v>114</v>
+        <v>79</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>115</v>
+        <v>276</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>116</v>
+        <v>100</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>79</v>
+        <v>277</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>79</v>
       </c>
     </row>
-    <row r="60" hidden="true">
+    <row r="60">
       <c r="A60" t="s" s="2">
-        <v>416</v>
+        <v>407</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>416</v>
+        <v>407</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8826,10 +8771,10 @@
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>89</v>
@@ -8841,19 +8786,17 @@
         <v>89</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>241</v>
+        <v>280</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>243</v>
-      </c>
+        <v>281</v>
+      </c>
+      <c r="N60" s="2"/>
       <c r="O60" t="s" s="2">
-        <v>244</v>
+        <v>282</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>79</v>
@@ -8890,23 +8833,25 @@
         <v>79</v>
       </c>
       <c r="AB60" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="AC60" s="2"/>
+        <v>79</v>
+      </c>
+      <c r="AC60" t="s" s="2">
+        <v>79</v>
+      </c>
       <c r="AD60" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE60" t="s" s="2">
-        <v>114</v>
+        <v>79</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>246</v>
+        <v>283</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>79</v>
@@ -8918,7 +8863,7 @@
         <v>79</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>247</v>
+        <v>284</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>79</v>
@@ -8926,10 +8871,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>417</v>
+        <v>408</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>417</v>
+        <v>408</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8949,19 +8894,23 @@
         <v>79</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>102</v>
+        <v>287</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>103</v>
+        <v>288</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="N61" s="2"/>
-      <c r="O61" s="2"/>
+        <v>289</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="O61" t="s" s="2">
+        <v>291</v>
+      </c>
       <c r="P61" t="s" s="2">
         <v>79</v>
       </c>
@@ -9009,7 +8958,7 @@
         <v>79</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>105</v>
+        <v>292</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>77</v>
@@ -9021,58 +8970,62 @@
         <v>79</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>79</v>
+        <v>293</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>79</v>
       </c>
     </row>
-    <row r="62" hidden="true">
+    <row r="62">
       <c r="A62" t="s" s="2">
-        <v>418</v>
+        <v>409</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="C62" s="2"/>
+        <v>401</v>
+      </c>
+      <c r="C62" t="s" s="2">
+        <v>410</v>
+      </c>
       <c r="D62" t="s" s="2">
-        <v>107</v>
+        <v>79</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H62" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="I62" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>108</v>
+        <v>141</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>109</v>
+        <v>241</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>110</v>
+        <v>242</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="O62" s="2"/>
+        <v>243</v>
+      </c>
+      <c r="O62" t="s" s="2">
+        <v>244</v>
+      </c>
       <c r="P62" t="s" s="2">
         <v>79</v>
       </c>
@@ -9081,7 +9034,7 @@
         <v>79</v>
       </c>
       <c r="S62" t="s" s="2">
-        <v>79</v>
+        <v>411</v>
       </c>
       <c r="T62" t="s" s="2">
         <v>79</v>
@@ -9108,19 +9061,19 @@
         <v>79</v>
       </c>
       <c r="AB62" t="s" s="2">
-        <v>112</v>
+        <v>79</v>
       </c>
       <c r="AC62" t="s" s="2">
-        <v>113</v>
+        <v>79</v>
       </c>
       <c r="AD62" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE62" t="s" s="2">
-        <v>114</v>
+        <v>79</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>115</v>
+        <v>246</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>77</v>
@@ -9132,24 +9085,24 @@
         <v>79</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>116</v>
+        <v>100</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>79</v>
+        <v>247</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>79</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>419</v>
+        <v>412</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>419</v>
+        <v>402</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9157,35 +9110,31 @@
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="G63" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H63" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="I63" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>129</v>
+        <v>102</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>256</v>
+        <v>103</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>257</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>258</v>
-      </c>
-      <c r="O63" t="s" s="2">
-        <v>259</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="N63" s="2"/>
+      <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>79</v>
       </c>
@@ -9233,7 +9182,7 @@
         <v>79</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>261</v>
+        <v>105</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>77</v>
@@ -9245,13 +9194,13 @@
         <v>79</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>100</v>
+        <v>79</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>262</v>
+        <v>79</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>79</v>
@@ -9259,21 +9208,21 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>420</v>
+        <v>413</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>420</v>
+        <v>403</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>79</v>
+        <v>107</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>79</v>
@@ -9282,19 +9231,19 @@
         <v>79</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>265</v>
+        <v>109</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>266</v>
+        <v>110</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>267</v>
+        <v>111</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -9332,37 +9281,37 @@
         <v>79</v>
       </c>
       <c r="AB64" t="s" s="2">
-        <v>79</v>
+        <v>112</v>
       </c>
       <c r="AC64" t="s" s="2">
-        <v>79</v>
+        <v>113</v>
       </c>
       <c r="AD64" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE64" t="s" s="2">
-        <v>79</v>
+        <v>114</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>268</v>
+        <v>115</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>100</v>
+        <v>116</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>269</v>
+        <v>79</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>79</v>
@@ -9370,10 +9319,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>421</v>
+        <v>414</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>421</v>
+        <v>404</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9396,17 +9345,19 @@
         <v>89</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>163</v>
+        <v>129</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>272</v>
+        <v>256</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="N65" s="2"/>
+        <v>257</v>
+      </c>
+      <c r="N65" t="s" s="2">
+        <v>258</v>
+      </c>
       <c r="O65" t="s" s="2">
-        <v>274</v>
+        <v>259</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>79</v>
@@ -9455,7 +9406,7 @@
         <v>79</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>276</v>
+        <v>261</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>77</v>
@@ -9473,18 +9424,18 @@
         <v>79</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>277</v>
+        <v>262</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>79</v>
       </c>
     </row>
-    <row r="66">
+    <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>422</v>
+        <v>415</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>422</v>
+        <v>405</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9498,7 +9449,7 @@
         <v>88</v>
       </c>
       <c r="H66" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="I66" t="s" s="2">
         <v>79</v>
@@ -9510,15 +9461,15 @@
         <v>102</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>280</v>
+        <v>265</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="N66" s="2"/>
-      <c r="O66" t="s" s="2">
-        <v>282</v>
-      </c>
+        <v>266</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>79</v>
       </c>
@@ -9566,7 +9517,7 @@
         <v>79</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>283</v>
+        <v>268</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>77</v>
@@ -9584,18 +9535,18 @@
         <v>79</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>284</v>
+        <v>269</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>79</v>
       </c>
     </row>
-    <row r="67" hidden="true">
+    <row r="67">
       <c r="A67" t="s" s="2">
-        <v>423</v>
+        <v>416</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>423</v>
+        <v>406</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9603,13 +9554,13 @@
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="G67" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H67" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="I67" t="s" s="2">
         <v>79</v>
@@ -9618,19 +9569,17 @@
         <v>89</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>287</v>
+        <v>163</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>288</v>
+        <v>272</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>290</v>
-      </c>
+        <v>273</v>
+      </c>
+      <c r="N67" s="2"/>
       <c r="O67" t="s" s="2">
-        <v>291</v>
+        <v>274</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>79</v>
@@ -9679,7 +9628,7 @@
         <v>79</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>292</v>
+        <v>276</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>77</v>
@@ -9697,7 +9646,7 @@
         <v>79</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>293</v>
+        <v>277</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>79</v>
@@ -9705,20 +9654,18 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>424</v>
+        <v>417</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="C68" t="s" s="2">
-        <v>425</v>
-      </c>
+        <v>407</v>
+      </c>
+      <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
         <v>79</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="G68" t="s" s="2">
         <v>88</v>
@@ -9733,19 +9680,17 @@
         <v>89</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>241</v>
+        <v>280</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="N68" t="s" s="2">
-        <v>243</v>
-      </c>
+        <v>281</v>
+      </c>
+      <c r="N68" s="2"/>
       <c r="O68" t="s" s="2">
-        <v>244</v>
+        <v>282</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>79</v>
@@ -9755,7 +9700,7 @@
         <v>79</v>
       </c>
       <c r="S68" t="s" s="2">
-        <v>426</v>
+        <v>79</v>
       </c>
       <c r="T68" t="s" s="2">
         <v>79</v>
@@ -9794,13 +9739,13 @@
         <v>79</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>246</v>
+        <v>283</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>79</v>
@@ -9812,7 +9757,7 @@
         <v>79</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>247</v>
+        <v>284</v>
       </c>
       <c r="AM68" t="s" s="2">
         <v>79</v>
@@ -9820,10 +9765,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>427</v>
+        <v>418</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>417</v>
+        <v>408</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9843,19 +9788,23 @@
         <v>79</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>102</v>
+        <v>287</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>103</v>
+        <v>288</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="N69" s="2"/>
-      <c r="O69" s="2"/>
+        <v>289</v>
+      </c>
+      <c r="N69" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="O69" t="s" s="2">
+        <v>291</v>
+      </c>
       <c r="P69" t="s" s="2">
         <v>79</v>
       </c>
@@ -9903,7 +9852,7 @@
         <v>79</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>105</v>
+        <v>292</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>77</v>
@@ -9915,13 +9864,13 @@
         <v>79</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>79</v>
+        <v>293</v>
       </c>
       <c r="AM69" t="s" s="2">
         <v>79</v>
@@ -9929,21 +9878,21 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>428</v>
+        <v>419</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>107</v>
+        <v>79</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>79</v>
@@ -9952,21 +9901,23 @@
         <v>79</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>109</v>
+        <v>296</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>110</v>
+        <v>297</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="O70" s="2"/>
+        <v>298</v>
+      </c>
+      <c r="O70" t="s" s="2">
+        <v>299</v>
+      </c>
       <c r="P70" t="s" s="2">
         <v>79</v>
       </c>
@@ -10002,37 +9953,37 @@
         <v>79</v>
       </c>
       <c r="AB70" t="s" s="2">
-        <v>112</v>
+        <v>79</v>
       </c>
       <c r="AC70" t="s" s="2">
-        <v>113</v>
+        <v>79</v>
       </c>
       <c r="AD70" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE70" t="s" s="2">
-        <v>114</v>
+        <v>79</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>115</v>
+        <v>300</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>116</v>
+        <v>100</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>79</v>
+        <v>301</v>
       </c>
       <c r="AM70" t="s" s="2">
         <v>79</v>
@@ -10040,14 +9991,14 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>429</v>
+        <v>420</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>79</v>
+        <v>421</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
@@ -10066,19 +10017,17 @@
         <v>89</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>129</v>
+        <v>422</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>256</v>
+        <v>423</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>257</v>
-      </c>
-      <c r="N71" t="s" s="2">
-        <v>258</v>
-      </c>
+        <v>424</v>
+      </c>
+      <c r="N71" s="2"/>
       <c r="O71" t="s" s="2">
-        <v>259</v>
+        <v>425</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>79</v>
@@ -10127,7 +10076,7 @@
         <v>79</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>261</v>
+        <v>420</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>77</v>
@@ -10142,21 +10091,21 @@
         <v>100</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>79</v>
+        <v>426</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>262</v>
+        <v>427</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>79</v>
+        <v>428</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>420</v>
+        <v>429</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10176,20 +10125,18 @@
         <v>79</v>
       </c>
       <c r="J72" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="K72" t="s" s="2">
         <v>102</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>265</v>
+        <v>103</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="N72" t="s" s="2">
-        <v>267</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="N72" s="2"/>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
         <v>79</v>
@@ -10238,7 +10185,7 @@
         <v>79</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>268</v>
+        <v>105</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>77</v>
@@ -10250,58 +10197,58 @@
         <v>79</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>100</v>
+        <v>79</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>269</v>
+        <v>79</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>79</v>
       </c>
     </row>
-    <row r="73">
+    <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>421</v>
+        <v>430</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>79</v>
+        <v>107</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H73" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="I73" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J73" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>163</v>
+        <v>108</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>272</v>
+        <v>109</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="N73" s="2"/>
-      <c r="O73" t="s" s="2">
-        <v>274</v>
-      </c>
+        <v>110</v>
+      </c>
+      <c r="N73" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
         <v>79</v>
       </c>
@@ -10337,37 +10284,37 @@
         <v>79</v>
       </c>
       <c r="AB73" t="s" s="2">
-        <v>79</v>
+        <v>112</v>
       </c>
       <c r="AC73" t="s" s="2">
-        <v>79</v>
+        <v>113</v>
       </c>
       <c r="AD73" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE73" t="s" s="2">
-        <v>79</v>
+        <v>114</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>276</v>
+        <v>115</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AI73" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>100</v>
+        <v>116</v>
       </c>
       <c r="AK73" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>277</v>
+        <v>79</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>79</v>
@@ -10375,10 +10322,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>422</v>
+        <v>431</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10404,15 +10351,15 @@
         <v>102</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>280</v>
+        <v>346</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="N74" s="2"/>
-      <c r="O74" t="s" s="2">
-        <v>282</v>
-      </c>
+        <v>347</v>
+      </c>
+      <c r="N74" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
         <v>79</v>
       </c>
@@ -10460,7 +10407,7 @@
         <v>79</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>283</v>
+        <v>349</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>77</v>
@@ -10469,7 +10416,7 @@
         <v>88</v>
       </c>
       <c r="AI74" t="s" s="2">
-        <v>79</v>
+        <v>350</v>
       </c>
       <c r="AJ74" t="s" s="2">
         <v>100</v>
@@ -10478,7 +10425,7 @@
         <v>79</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>284</v>
+        <v>79</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>79</v>
@@ -10486,10 +10433,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>423</v>
+        <v>432</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10512,20 +10459,18 @@
         <v>89</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>287</v>
+        <v>129</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>288</v>
+        <v>352</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>289</v>
+        <v>353</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>290</v>
-      </c>
-      <c r="O75" t="s" s="2">
-        <v>291</v>
-      </c>
+        <v>354</v>
+      </c>
+      <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
         <v>79</v>
       </c>
@@ -10549,13 +10494,13 @@
         <v>79</v>
       </c>
       <c r="X75" t="s" s="2">
-        <v>79</v>
+        <v>145</v>
       </c>
       <c r="Y75" t="s" s="2">
-        <v>79</v>
+        <v>355</v>
       </c>
       <c r="Z75" t="s" s="2">
-        <v>79</v>
+        <v>356</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>79</v>
@@ -10573,7 +10518,7 @@
         <v>79</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>292</v>
+        <v>357</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>77</v>
@@ -10591,18 +10536,18 @@
         <v>79</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>293</v>
+        <v>79</v>
       </c>
       <c r="AM75" t="s" s="2">
         <v>79</v>
       </c>
     </row>
-    <row r="76" hidden="true">
+    <row r="76">
       <c r="A76" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10616,7 +10561,7 @@
         <v>88</v>
       </c>
       <c r="H76" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="I76" t="s" s="2">
         <v>79</v>
@@ -10625,20 +10570,18 @@
         <v>89</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>102</v>
+        <v>195</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>296</v>
+        <v>359</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>297</v>
+        <v>360</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>298</v>
-      </c>
-      <c r="O76" t="s" s="2">
-        <v>299</v>
-      </c>
+        <v>361</v>
+      </c>
+      <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
         <v>79</v>
       </c>
@@ -10686,7 +10629,7 @@
         <v>79</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>300</v>
+        <v>362</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>77</v>
@@ -10704,32 +10647,32 @@
         <v>79</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>301</v>
+        <v>79</v>
       </c>
       <c r="AM76" t="s" s="2">
         <v>79</v>
       </c>
     </row>
-    <row r="77">
+    <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>436</v>
+        <v>79</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="G77" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H77" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="I77" t="s" s="2">
         <v>79</v>
@@ -10738,18 +10681,18 @@
         <v>89</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>437</v>
+        <v>102</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>438</v>
+        <v>364</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="N77" s="2"/>
-      <c r="O77" t="s" s="2">
-        <v>440</v>
-      </c>
+        <v>365</v>
+      </c>
+      <c r="N77" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
         <v>79</v>
       </c>
@@ -10797,7 +10740,7 @@
         <v>79</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>435</v>
+        <v>367</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>77</v>
@@ -10812,25 +10755,25 @@
         <v>100</v>
       </c>
       <c r="AK77" t="s" s="2">
-        <v>441</v>
+        <v>79</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>442</v>
+        <v>79</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>443</v>
+        <v>79</v>
       </c>
     </row>
-    <row r="78" hidden="true">
+    <row r="78">
       <c r="A78" t="s" s="2">
-        <v>444</v>
+        <v>435</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>444</v>
+        <v>435</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
-        <v>79</v>
+        <v>436</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
@@ -10840,25 +10783,29 @@
         <v>88</v>
       </c>
       <c r="H78" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="I78" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J78" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>102</v>
+        <v>437</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>103</v>
+        <v>438</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="N78" s="2"/>
-      <c r="O78" s="2"/>
+        <v>439</v>
+      </c>
+      <c r="N78" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="O78" t="s" s="2">
+        <v>441</v>
+      </c>
       <c r="P78" t="s" s="2">
         <v>79</v>
       </c>
@@ -10906,7 +10853,7 @@
         <v>79</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>105</v>
+        <v>435</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>77</v>
@@ -10918,16 +10865,16 @@
         <v>79</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="AK78" t="s" s="2">
-        <v>79</v>
+        <v>442</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>79</v>
+        <v>443</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>79</v>
+        <v>444</v>
       </c>
     </row>
     <row r="79" hidden="true">
@@ -10939,14 +10886,14 @@
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
-        <v>107</v>
+        <v>79</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H79" t="s" s="2">
         <v>79</v>
@@ -10958,17 +10905,15 @@
         <v>79</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="N79" t="s" s="2">
-        <v>111</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="N79" s="2"/>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
         <v>79</v>
@@ -11005,31 +10950,31 @@
         <v>79</v>
       </c>
       <c r="AB79" t="s" s="2">
-        <v>112</v>
+        <v>79</v>
       </c>
       <c r="AC79" t="s" s="2">
-        <v>113</v>
+        <v>79</v>
       </c>
       <c r="AD79" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE79" t="s" s="2">
-        <v>114</v>
+        <v>79</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH79" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AI79" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>116</v>
+        <v>79</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>79</v>
@@ -11041,7 +10986,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="80">
+    <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
         <v>446</v>
       </c>
@@ -11050,35 +10995,35 @@
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
-        <v>79</v>
+        <v>107</v>
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G80" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H80" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="I80" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J80" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>346</v>
+        <v>109</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>347</v>
+        <v>110</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>348</v>
+        <v>111</v>
       </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
@@ -11116,31 +11061,31 @@
         <v>79</v>
       </c>
       <c r="AB80" t="s" s="2">
-        <v>79</v>
+        <v>112</v>
       </c>
       <c r="AC80" t="s" s="2">
-        <v>79</v>
+        <v>113</v>
       </c>
       <c r="AD80" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE80" t="s" s="2">
-        <v>79</v>
+        <v>114</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>349</v>
+        <v>115</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH80" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AI80" t="s" s="2">
-        <v>350</v>
+        <v>79</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>100</v>
+        <v>116</v>
       </c>
       <c r="AK80" t="s" s="2">
         <v>79</v>
@@ -11152,7 +11097,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="81" hidden="true">
+    <row r="81">
       <c r="A81" t="s" s="2">
         <v>447</v>
       </c>
@@ -11171,7 +11116,7 @@
         <v>88</v>
       </c>
       <c r="H81" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="I81" t="s" s="2">
         <v>79</v>
@@ -11180,16 +11125,16 @@
         <v>89</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>129</v>
+        <v>102</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>354</v>
+        <v>348</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -11215,13 +11160,13 @@
         <v>79</v>
       </c>
       <c r="X81" t="s" s="2">
-        <v>145</v>
+        <v>79</v>
       </c>
       <c r="Y81" t="s" s="2">
-        <v>355</v>
+        <v>79</v>
       </c>
       <c r="Z81" t="s" s="2">
-        <v>356</v>
+        <v>79</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>79</v>
@@ -11239,7 +11184,7 @@
         <v>79</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>357</v>
+        <v>349</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>77</v>
@@ -11248,7 +11193,7 @@
         <v>88</v>
       </c>
       <c r="AI81" t="s" s="2">
-        <v>79</v>
+        <v>350</v>
       </c>
       <c r="AJ81" t="s" s="2">
         <v>100</v>
@@ -11263,7 +11208,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="82">
+    <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
         <v>448</v>
       </c>
@@ -11282,7 +11227,7 @@
         <v>88</v>
       </c>
       <c r="H82" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="I82" t="s" s="2">
         <v>79</v>
@@ -11291,16 +11236,16 @@
         <v>89</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>195</v>
+        <v>129</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>359</v>
+        <v>352</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>360</v>
+        <v>353</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>361</v>
+        <v>354</v>
       </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
@@ -11326,13 +11271,13 @@
         <v>79</v>
       </c>
       <c r="X82" t="s" s="2">
-        <v>79</v>
+        <v>145</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>79</v>
+        <v>355</v>
       </c>
       <c r="Z82" t="s" s="2">
-        <v>79</v>
+        <v>356</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>79</v>
@@ -11350,7 +11295,7 @@
         <v>79</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>77</v>
@@ -11374,7 +11319,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="83" hidden="true">
+    <row r="83">
       <c r="A83" t="s" s="2">
         <v>449</v>
       </c>
@@ -11393,7 +11338,7 @@
         <v>88</v>
       </c>
       <c r="H83" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="I83" t="s" s="2">
         <v>79</v>
@@ -11402,16 +11347,16 @@
         <v>89</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>102</v>
+        <v>195</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
@@ -11461,7 +11406,7 @@
         <v>79</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>77</v>
@@ -11485,7 +11430,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="84">
+    <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
         <v>450</v>
       </c>
@@ -11494,7 +11439,7 @@
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
-        <v>451</v>
+        <v>79</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
@@ -11504,7 +11449,7 @@
         <v>88</v>
       </c>
       <c r="H84" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="I84" t="s" s="2">
         <v>79</v>
@@ -11513,20 +11458,18 @@
         <v>89</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>452</v>
+        <v>102</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>453</v>
+        <v>364</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>454</v>
+        <v>365</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>455</v>
-      </c>
-      <c r="O84" t="s" s="2">
-        <v>456</v>
-      </c>
+        <v>366</v>
+      </c>
+      <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
         <v>79</v>
       </c>
@@ -11574,7 +11517,7 @@
         <v>79</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>450</v>
+        <v>367</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>77</v>
@@ -11589,53 +11532,57 @@
         <v>100</v>
       </c>
       <c r="AK84" t="s" s="2">
-        <v>457</v>
+        <v>79</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>458</v>
+        <v>79</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>459</v>
+        <v>79</v>
       </c>
     </row>
-    <row r="85" hidden="true">
+    <row r="85">
       <c r="A85" t="s" s="2">
-        <v>460</v>
+        <v>451</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>460</v>
+        <v>451</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
-        <v>79</v>
+        <v>452</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="G85" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H85" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="I85" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J85" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>102</v>
+        <v>453</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>103</v>
+        <v>454</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="N85" s="2"/>
-      <c r="O85" s="2"/>
+        <v>455</v>
+      </c>
+      <c r="N85" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="O85" t="s" s="2">
+        <v>457</v>
+      </c>
       <c r="P85" t="s" s="2">
         <v>79</v>
       </c>
@@ -11683,7 +11630,7 @@
         <v>79</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>105</v>
+        <v>451</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>77</v>
@@ -11695,16 +11642,16 @@
         <v>79</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="AK85" t="s" s="2">
-        <v>79</v>
+        <v>458</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>79</v>
+        <v>459</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>79</v>
+        <v>460</v>
       </c>
     </row>
     <row r="86" hidden="true">
@@ -11716,14 +11663,14 @@
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
-        <v>107</v>
+        <v>79</v>
       </c>
       <c r="E86" s="2"/>
       <c r="F86" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G86" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H86" t="s" s="2">
         <v>79</v>
@@ -11735,17 +11682,15 @@
         <v>79</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>109</v>
+        <v>462</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="N86" t="s" s="2">
-        <v>111</v>
-      </c>
+        <v>463</v>
+      </c>
+      <c r="N86" s="2"/>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
         <v>79</v>
@@ -11782,31 +11727,31 @@
         <v>79</v>
       </c>
       <c r="AB86" t="s" s="2">
-        <v>112</v>
+        <v>79</v>
       </c>
       <c r="AC86" t="s" s="2">
-        <v>113</v>
+        <v>79</v>
       </c>
       <c r="AD86" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE86" t="s" s="2">
-        <v>114</v>
+        <v>79</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH86" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AI86" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>116</v>
+        <v>79</v>
       </c>
       <c r="AK86" t="s" s="2">
         <v>79</v>
@@ -11818,12 +11763,12 @@
         <v>79</v>
       </c>
     </row>
-    <row r="87">
+    <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -11834,29 +11779,27 @@
         <v>77</v>
       </c>
       <c r="G87" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H87" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="I87" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J87" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>346</v>
+        <v>465</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>347</v>
-      </c>
-      <c r="N87" t="s" s="2">
-        <v>348</v>
-      </c>
+        <v>466</v>
+      </c>
+      <c r="N87" s="2"/>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
         <v>79</v>
@@ -11893,31 +11836,29 @@
         <v>79</v>
       </c>
       <c r="AB87" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC87" t="s" s="2">
-        <v>79</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="AC87" s="2"/>
       <c r="AD87" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE87" t="s" s="2">
-        <v>79</v>
+        <v>114</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>349</v>
+        <v>115</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH87" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AI87" t="s" s="2">
-        <v>350</v>
+        <v>79</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>100</v>
+        <v>116</v>
       </c>
       <c r="AK87" t="s" s="2">
         <v>79</v>
@@ -11929,14 +11870,16 @@
         <v>79</v>
       </c>
     </row>
-    <row r="88" hidden="true">
+    <row r="88">
       <c r="A88" t="s" s="2">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>463</v>
-      </c>
-      <c r="C88" s="2"/>
+        <v>464</v>
+      </c>
+      <c r="C88" t="s" s="2">
+        <v>468</v>
+      </c>
       <c r="D88" t="s" s="2">
         <v>79</v>
       </c>
@@ -11948,26 +11891,24 @@
         <v>88</v>
       </c>
       <c r="H88" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="I88" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J88" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>129</v>
+        <v>469</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>352</v>
+        <v>470</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>353</v>
-      </c>
-      <c r="N88" t="s" s="2">
-        <v>354</v>
-      </c>
+        <v>471</v>
+      </c>
+      <c r="N88" s="2"/>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
         <v>79</v>
@@ -11992,13 +11933,13 @@
         <v>79</v>
       </c>
       <c r="X88" t="s" s="2">
-        <v>145</v>
+        <v>79</v>
       </c>
       <c r="Y88" t="s" s="2">
-        <v>355</v>
+        <v>79</v>
       </c>
       <c r="Z88" t="s" s="2">
-        <v>356</v>
+        <v>79</v>
       </c>
       <c r="AA88" t="s" s="2">
         <v>79</v>
@@ -12016,19 +11957,19 @@
         <v>79</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>357</v>
+        <v>115</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH88" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AI88" t="s" s="2">
-        <v>79</v>
+        <v>472</v>
       </c>
       <c r="AJ88" t="s" s="2">
-        <v>100</v>
+        <v>116</v>
       </c>
       <c r="AK88" t="s" s="2">
         <v>79</v>
@@ -12040,12 +11981,12 @@
         <v>79</v>
       </c>
     </row>
-    <row r="89">
+    <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>464</v>
+        <v>473</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>464</v>
+        <v>473</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12059,26 +12000,24 @@
         <v>88</v>
       </c>
       <c r="H89" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="I89" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J89" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>195</v>
+        <v>453</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>359</v>
+        <v>474</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>360</v>
-      </c>
-      <c r="N89" t="s" s="2">
-        <v>361</v>
-      </c>
+        <v>475</v>
+      </c>
+      <c r="N89" s="2"/>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
         <v>79</v>
@@ -12127,7 +12066,7 @@
         <v>79</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>362</v>
+        <v>476</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>77</v>
@@ -12139,7 +12078,7 @@
         <v>79</v>
       </c>
       <c r="AJ89" t="s" s="2">
-        <v>100</v>
+        <v>79</v>
       </c>
       <c r="AK89" t="s" s="2">
         <v>79</v>
@@ -12151,26 +12090,26 @@
         <v>79</v>
       </c>
     </row>
-    <row r="90" hidden="true">
+    <row r="90">
       <c r="A90" t="s" s="2">
-        <v>465</v>
+        <v>477</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>465</v>
+        <v>477</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
-        <v>79</v>
+        <v>478</v>
       </c>
       <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="G90" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H90" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="I90" t="s" s="2">
         <v>79</v>
@@ -12179,18 +12118,20 @@
         <v>89</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>102</v>
+        <v>123</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>364</v>
+        <v>479</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>365</v>
+        <v>480</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>366</v>
-      </c>
-      <c r="O90" s="2"/>
+        <v>481</v>
+      </c>
+      <c r="O90" t="s" s="2">
+        <v>482</v>
+      </c>
       <c r="P90" t="s" s="2">
         <v>79</v>
       </c>
@@ -12238,7 +12179,7 @@
         <v>79</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>367</v>
+        <v>477</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>77</v>
@@ -12256,29 +12197,29 @@
         <v>79</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>79</v>
+        <v>483</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>79</v>
+        <v>484</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>466</v>
+        <v>485</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>466</v>
+        <v>485</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
-        <v>467</v>
+        <v>486</v>
       </c>
       <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="G91" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H91" t="s" s="2">
         <v>89</v>
@@ -12290,19 +12231,19 @@
         <v>89</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>468</v>
+        <v>487</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>469</v>
+        <v>488</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>470</v>
+        <v>489</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>471</v>
+        <v>490</v>
       </c>
       <c r="O91" t="s" s="2">
-        <v>472</v>
+        <v>491</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>79</v>
@@ -12351,13 +12292,13 @@
         <v>79</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>466</v>
+        <v>485</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH91" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AI91" t="s" s="2">
         <v>79</v>
@@ -12366,21 +12307,21 @@
         <v>100</v>
       </c>
       <c r="AK91" t="s" s="2">
-        <v>473</v>
+        <v>492</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>474</v>
+        <v>493</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>475</v>
+        <v>494</v>
       </c>
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>476</v>
+        <v>495</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>476</v>
+        <v>495</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -12406,10 +12347,10 @@
         <v>102</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>477</v>
+        <v>103</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>478</v>
+        <v>104</v>
       </c>
       <c r="N92" s="2"/>
       <c r="O92" s="2"/>
@@ -12486,14 +12427,14 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>479</v>
+        <v>496</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>479</v>
+        <v>496</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
-        <v>79</v>
+        <v>107</v>
       </c>
       <c r="E93" s="2"/>
       <c r="F93" t="s" s="2">
@@ -12515,12 +12456,14 @@
         <v>108</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>480</v>
+        <v>109</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>481</v>
-      </c>
-      <c r="N93" s="2"/>
+        <v>110</v>
+      </c>
+      <c r="N93" t="s" s="2">
+        <v>111</v>
+      </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
         <v>79</v>
@@ -12559,7 +12502,9 @@
       <c r="AB93" t="s" s="2">
         <v>112</v>
       </c>
-      <c r="AC93" s="2"/>
+      <c r="AC93" t="s" s="2">
+        <v>113</v>
+      </c>
       <c r="AD93" t="s" s="2">
         <v>79</v>
       </c>
@@ -12593,14 +12538,12 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>482</v>
+        <v>497</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>479</v>
-      </c>
-      <c r="C94" t="s" s="2">
-        <v>483</v>
-      </c>
+        <v>497</v>
+      </c>
+      <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
         <v>79</v>
       </c>
@@ -12618,18 +12561,20 @@
         <v>79</v>
       </c>
       <c r="J94" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>484</v>
+        <v>102</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>485</v>
+        <v>346</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>486</v>
-      </c>
-      <c r="N94" s="2"/>
+        <v>347</v>
+      </c>
+      <c r="N94" t="s" s="2">
+        <v>348</v>
+      </c>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
         <v>79</v>
@@ -12678,19 +12623,19 @@
         <v>79</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>115</v>
+        <v>349</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH94" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AI94" t="s" s="2">
-        <v>487</v>
+        <v>350</v>
       </c>
       <c r="AJ94" t="s" s="2">
-        <v>116</v>
+        <v>100</v>
       </c>
       <c r="AK94" t="s" s="2">
         <v>79</v>
@@ -12704,10 +12649,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>488</v>
+        <v>498</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>488</v>
+        <v>498</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -12727,18 +12672,20 @@
         <v>79</v>
       </c>
       <c r="J95" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>468</v>
+        <v>129</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>489</v>
+        <v>352</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>490</v>
-      </c>
-      <c r="N95" s="2"/>
+        <v>353</v>
+      </c>
+      <c r="N95" t="s" s="2">
+        <v>354</v>
+      </c>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
         <v>79</v>
@@ -12763,13 +12710,13 @@
         <v>79</v>
       </c>
       <c r="X95" t="s" s="2">
-        <v>79</v>
+        <v>145</v>
       </c>
       <c r="Y95" t="s" s="2">
-        <v>79</v>
+        <v>355</v>
       </c>
       <c r="Z95" t="s" s="2">
-        <v>79</v>
+        <v>356</v>
       </c>
       <c r="AA95" t="s" s="2">
         <v>79</v>
@@ -12787,7 +12734,7 @@
         <v>79</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>491</v>
+        <v>357</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>77</v>
@@ -12799,7 +12746,7 @@
         <v>79</v>
       </c>
       <c r="AJ95" t="s" s="2">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="AK95" t="s" s="2">
         <v>79</v>
@@ -12813,18 +12760,18 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>492</v>
+        <v>499</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>492</v>
+        <v>499</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
-        <v>493</v>
+        <v>79</v>
       </c>
       <c r="E96" s="2"/>
       <c r="F96" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="G96" t="s" s="2">
         <v>88</v>
@@ -12839,20 +12786,18 @@
         <v>89</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>123</v>
+        <v>195</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>494</v>
+        <v>359</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>495</v>
+        <v>360</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>496</v>
-      </c>
-      <c r="O96" t="s" s="2">
-        <v>497</v>
-      </c>
+        <v>361</v>
+      </c>
+      <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
         <v>79</v>
       </c>
@@ -12900,7 +12845,7 @@
         <v>79</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>492</v>
+        <v>362</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>77</v>
@@ -12918,13 +12863,13 @@
         <v>79</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>498</v>
+        <v>79</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>499</v>
+        <v>79</v>
       </c>
     </row>
-    <row r="97">
+    <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
         <v>500</v>
       </c>
@@ -12933,17 +12878,17 @@
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
-        <v>501</v>
+        <v>79</v>
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G97" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H97" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="I97" t="s" s="2">
         <v>79</v>
@@ -12952,20 +12897,18 @@
         <v>89</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>502</v>
+        <v>102</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>503</v>
+        <v>364</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>504</v>
+        <v>365</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>505</v>
-      </c>
-      <c r="O97" t="s" s="2">
-        <v>506</v>
-      </c>
+        <v>366</v>
+      </c>
+      <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
         <v>79</v>
       </c>
@@ -13013,13 +12956,13 @@
         <v>79</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>500</v>
+        <v>367</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH97" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AI97" t="s" s="2">
         <v>79</v>
@@ -13028,32 +12971,32 @@
         <v>100</v>
       </c>
       <c r="AK97" t="s" s="2">
-        <v>507</v>
+        <v>79</v>
       </c>
       <c r="AL97" t="s" s="2">
-        <v>508</v>
+        <v>79</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>509</v>
+        <v>79</v>
       </c>
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>510</v>
+        <v>501</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>510</v>
+        <v>501</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
-        <v>79</v>
+        <v>502</v>
       </c>
       <c r="E98" s="2"/>
       <c r="F98" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G98" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H98" t="s" s="2">
         <v>79</v>
@@ -13062,19 +13005,23 @@
         <v>79</v>
       </c>
       <c r="J98" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>102</v>
+        <v>487</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>103</v>
+        <v>503</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="N98" s="2"/>
-      <c r="O98" s="2"/>
+        <v>504</v>
+      </c>
+      <c r="N98" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="O98" t="s" s="2">
+        <v>491</v>
+      </c>
       <c r="P98" t="s" s="2">
         <v>79</v>
       </c>
@@ -13122,40 +13069,40 @@
         <v>79</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>105</v>
+        <v>501</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH98" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AI98" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ98" t="s" s="2">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="AK98" t="s" s="2">
-        <v>79</v>
+        <v>492</v>
       </c>
       <c r="AL98" t="s" s="2">
-        <v>79</v>
+        <v>506</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>79</v>
+        <v>494</v>
       </c>
     </row>
-    <row r="99" hidden="true">
+    <row r="99">
       <c r="A99" t="s" s="2">
-        <v>511</v>
+        <v>507</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>511</v>
+        <v>507</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
-        <v>107</v>
+        <v>79</v>
       </c>
       <c r="E99" s="2"/>
       <c r="F99" t="s" s="2">
@@ -13165,7 +13112,7 @@
         <v>78</v>
       </c>
       <c r="H99" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="I99" t="s" s="2">
         <v>79</v>
@@ -13174,18 +13121,20 @@
         <v>79</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>108</v>
+        <v>508</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>109</v>
+        <v>509</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>110</v>
+        <v>510</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="O99" s="2"/>
+        <v>511</v>
+      </c>
+      <c r="O99" t="s" s="2">
+        <v>512</v>
+      </c>
       <c r="P99" t="s" s="2">
         <v>79</v>
       </c>
@@ -13221,19 +13170,19 @@
         <v>79</v>
       </c>
       <c r="AB99" t="s" s="2">
-        <v>112</v>
+        <v>79</v>
       </c>
       <c r="AC99" t="s" s="2">
-        <v>113</v>
+        <v>79</v>
       </c>
       <c r="AD99" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE99" t="s" s="2">
-        <v>114</v>
+        <v>79</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>115</v>
+        <v>507</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>77</v>
@@ -13245,24 +13194,24 @@
         <v>79</v>
       </c>
       <c r="AJ99" t="s" s="2">
-        <v>116</v>
+        <v>100</v>
       </c>
       <c r="AK99" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL99" t="s" s="2">
-        <v>79</v>
+        <v>513</v>
       </c>
       <c r="AM99" t="s" s="2">
         <v>79</v>
       </c>
     </row>
-    <row r="100">
+    <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -13276,26 +13225,24 @@
         <v>88</v>
       </c>
       <c r="H100" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="I100" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J100" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="K100" t="s" s="2">
         <v>102</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>346</v>
+        <v>103</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>347</v>
-      </c>
-      <c r="N100" t="s" s="2">
-        <v>348</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="N100" s="2"/>
       <c r="O100" s="2"/>
       <c r="P100" t="s" s="2">
         <v>79</v>
@@ -13344,7 +13291,7 @@
         <v>79</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>349</v>
+        <v>105</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>77</v>
@@ -13353,10 +13300,10 @@
         <v>88</v>
       </c>
       <c r="AI100" t="s" s="2">
-        <v>350</v>
+        <v>79</v>
       </c>
       <c r="AJ100" t="s" s="2">
-        <v>100</v>
+        <v>79</v>
       </c>
       <c r="AK100" t="s" s="2">
         <v>79</v>
@@ -13370,21 +13317,21 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
-        <v>79</v>
+        <v>107</v>
       </c>
       <c r="E101" s="2"/>
       <c r="F101" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G101" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H101" t="s" s="2">
         <v>79</v>
@@ -13393,19 +13340,19 @@
         <v>79</v>
       </c>
       <c r="J101" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>129</v>
+        <v>108</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>352</v>
+        <v>109</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>353</v>
+        <v>110</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>354</v>
+        <v>111</v>
       </c>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
@@ -13431,43 +13378,43 @@
         <v>79</v>
       </c>
       <c r="X101" t="s" s="2">
-        <v>145</v>
+        <v>79</v>
       </c>
       <c r="Y101" t="s" s="2">
-        <v>355</v>
+        <v>79</v>
       </c>
       <c r="Z101" t="s" s="2">
-        <v>356</v>
+        <v>79</v>
       </c>
       <c r="AA101" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AB101" t="s" s="2">
-        <v>79</v>
+        <v>112</v>
       </c>
       <c r="AC101" t="s" s="2">
-        <v>79</v>
+        <v>113</v>
       </c>
       <c r="AD101" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE101" t="s" s="2">
-        <v>79</v>
+        <v>114</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>357</v>
+        <v>115</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH101" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AI101" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ101" t="s" s="2">
-        <v>100</v>
+        <v>116</v>
       </c>
       <c r="AK101" t="s" s="2">
         <v>79</v>
@@ -13481,10 +13428,10 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -13507,16 +13454,16 @@
         <v>89</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>195</v>
+        <v>102</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>359</v>
+        <v>346</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>360</v>
+        <v>347</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>361</v>
+        <v>348</v>
       </c>
       <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
@@ -13566,7 +13513,7 @@
         <v>79</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>362</v>
+        <v>349</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>77</v>
@@ -13575,7 +13522,7 @@
         <v>88</v>
       </c>
       <c r="AI102" t="s" s="2">
-        <v>79</v>
+        <v>350</v>
       </c>
       <c r="AJ102" t="s" s="2">
         <v>100</v>
@@ -13592,10 +13539,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -13618,16 +13565,16 @@
         <v>89</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>102</v>
+        <v>129</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>364</v>
+        <v>352</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>365</v>
+        <v>353</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>366</v>
+        <v>354</v>
       </c>
       <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
@@ -13653,13 +13600,13 @@
         <v>79</v>
       </c>
       <c r="X103" t="s" s="2">
-        <v>79</v>
+        <v>145</v>
       </c>
       <c r="Y103" t="s" s="2">
-        <v>79</v>
+        <v>355</v>
       </c>
       <c r="Z103" t="s" s="2">
-        <v>79</v>
+        <v>356</v>
       </c>
       <c r="AA103" t="s" s="2">
         <v>79</v>
@@ -13677,7 +13624,7 @@
         <v>79</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>367</v>
+        <v>357</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>77</v>
@@ -13701,26 +13648,26 @@
         <v>79</v>
       </c>
     </row>
-    <row r="104" hidden="true">
+    <row r="104">
       <c r="A104" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
-        <v>517</v>
+        <v>79</v>
       </c>
       <c r="E104" s="2"/>
       <c r="F104" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G104" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H104" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="I104" t="s" s="2">
         <v>79</v>
@@ -13729,20 +13676,18 @@
         <v>89</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>502</v>
+        <v>195</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>518</v>
+        <v>359</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>519</v>
+        <v>360</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>520</v>
-      </c>
-      <c r="O104" t="s" s="2">
-        <v>506</v>
-      </c>
+        <v>361</v>
+      </c>
+      <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
         <v>79</v>
       </c>
@@ -13790,13 +13735,13 @@
         <v>79</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>516</v>
+        <v>362</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH104" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AI104" t="s" s="2">
         <v>79</v>
@@ -13805,21 +13750,21 @@
         <v>100</v>
       </c>
       <c r="AK104" t="s" s="2">
-        <v>507</v>
+        <v>79</v>
       </c>
       <c r="AL104" t="s" s="2">
-        <v>521</v>
+        <v>79</v>
       </c>
       <c r="AM104" t="s" s="2">
-        <v>509</v>
+        <v>79</v>
       </c>
     </row>
-    <row r="105">
+    <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -13830,32 +13775,30 @@
         <v>77</v>
       </c>
       <c r="G105" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H105" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I105" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J105" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="I105" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J105" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="K105" t="s" s="2">
-        <v>523</v>
+        <v>102</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>524</v>
+        <v>364</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>525</v>
+        <v>365</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>526</v>
-      </c>
-      <c r="O105" t="s" s="2">
-        <v>527</v>
-      </c>
+        <v>366</v>
+      </c>
+      <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
         <v>79</v>
       </c>
@@ -13903,13 +13846,13 @@
         <v>79</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>522</v>
+        <v>367</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH105" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AI105" t="s" s="2">
         <v>79</v>
@@ -13921,32 +13864,32 @@
         <v>79</v>
       </c>
       <c r="AL105" t="s" s="2">
-        <v>528</v>
+        <v>79</v>
       </c>
       <c r="AM105" t="s" s="2">
         <v>79</v>
       </c>
     </row>
-    <row r="106" hidden="true">
+    <row r="106">
       <c r="A106" t="s" s="2">
-        <v>529</v>
+        <v>520</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>529</v>
+        <v>520</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
-        <v>79</v>
+        <v>521</v>
       </c>
       <c r="E106" s="2"/>
       <c r="F106" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="G106" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H106" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="I106" t="s" s="2">
         <v>79</v>
@@ -13955,16 +13898,20 @@
         <v>79</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>102</v>
+        <v>522</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>103</v>
+        <v>523</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="N106" s="2"/>
-      <c r="O106" s="2"/>
+        <v>524</v>
+      </c>
+      <c r="N106" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="O106" t="s" s="2">
+        <v>526</v>
+      </c>
       <c r="P106" t="s" s="2">
         <v>79</v>
       </c>
@@ -14012,25 +13959,25 @@
         <v>79</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>105</v>
+        <v>520</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH106" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AI106" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ106" t="s" s="2">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="AK106" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL106" t="s" s="2">
-        <v>79</v>
+        <v>527</v>
       </c>
       <c r="AM106" t="s" s="2">
         <v>79</v>
@@ -14038,21 +13985,21 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
-        <v>107</v>
+        <v>79</v>
       </c>
       <c r="E107" s="2"/>
       <c r="F107" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G107" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H107" t="s" s="2">
         <v>79</v>
@@ -14064,17 +14011,15 @@
         <v>79</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="N107" t="s" s="2">
-        <v>111</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="N107" s="2"/>
       <c r="O107" s="2"/>
       <c r="P107" t="s" s="2">
         <v>79</v>
@@ -14111,31 +14056,31 @@
         <v>79</v>
       </c>
       <c r="AB107" t="s" s="2">
-        <v>112</v>
+        <v>79</v>
       </c>
       <c r="AC107" t="s" s="2">
-        <v>113</v>
+        <v>79</v>
       </c>
       <c r="AD107" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE107" t="s" s="2">
-        <v>114</v>
+        <v>79</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH107" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AI107" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ107" t="s" s="2">
-        <v>116</v>
+        <v>79</v>
       </c>
       <c r="AK107" t="s" s="2">
         <v>79</v>
@@ -14147,44 +14092,44 @@
         <v>79</v>
       </c>
     </row>
-    <row r="108">
+    <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
-        <v>79</v>
+        <v>107</v>
       </c>
       <c r="E108" s="2"/>
       <c r="F108" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G108" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H108" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="I108" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J108" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>346</v>
+        <v>109</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>347</v>
+        <v>110</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>348</v>
+        <v>111</v>
       </c>
       <c r="O108" s="2"/>
       <c r="P108" t="s" s="2">
@@ -14222,31 +14167,31 @@
         <v>79</v>
       </c>
       <c r="AB108" t="s" s="2">
-        <v>79</v>
+        <v>112</v>
       </c>
       <c r="AC108" t="s" s="2">
-        <v>79</v>
+        <v>113</v>
       </c>
       <c r="AD108" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE108" t="s" s="2">
-        <v>79</v>
+        <v>114</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>349</v>
+        <v>115</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH108" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AI108" t="s" s="2">
-        <v>350</v>
+        <v>79</v>
       </c>
       <c r="AJ108" t="s" s="2">
-        <v>100</v>
+        <v>116</v>
       </c>
       <c r="AK108" t="s" s="2">
         <v>79</v>
@@ -14258,12 +14203,12 @@
         <v>79</v>
       </c>
     </row>
-    <row r="109" hidden="true">
+    <row r="109">
       <c r="A109" t="s" s="2">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -14277,7 +14222,7 @@
         <v>88</v>
       </c>
       <c r="H109" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="I109" t="s" s="2">
         <v>79</v>
@@ -14286,16 +14231,16 @@
         <v>89</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>129</v>
+        <v>102</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>354</v>
+        <v>348</v>
       </c>
       <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
@@ -14321,13 +14266,13 @@
         <v>79</v>
       </c>
       <c r="X109" t="s" s="2">
-        <v>145</v>
+        <v>79</v>
       </c>
       <c r="Y109" t="s" s="2">
-        <v>355</v>
+        <v>79</v>
       </c>
       <c r="Z109" t="s" s="2">
-        <v>356</v>
+        <v>79</v>
       </c>
       <c r="AA109" t="s" s="2">
         <v>79</v>
@@ -14345,7 +14290,7 @@
         <v>79</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>357</v>
+        <v>349</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>77</v>
@@ -14354,7 +14299,7 @@
         <v>88</v>
       </c>
       <c r="AI109" t="s" s="2">
-        <v>79</v>
+        <v>350</v>
       </c>
       <c r="AJ109" t="s" s="2">
         <v>100</v>
@@ -14369,12 +14314,12 @@
         <v>79</v>
       </c>
     </row>
-    <row r="110">
+    <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -14388,7 +14333,7 @@
         <v>88</v>
       </c>
       <c r="H110" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="I110" t="s" s="2">
         <v>79</v>
@@ -14397,16 +14342,16 @@
         <v>89</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>195</v>
+        <v>129</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>359</v>
+        <v>352</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>360</v>
+        <v>353</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>361</v>
+        <v>354</v>
       </c>
       <c r="O110" s="2"/>
       <c r="P110" t="s" s="2">
@@ -14432,13 +14377,13 @@
         <v>79</v>
       </c>
       <c r="X110" t="s" s="2">
-        <v>79</v>
+        <v>145</v>
       </c>
       <c r="Y110" t="s" s="2">
-        <v>79</v>
+        <v>355</v>
       </c>
       <c r="Z110" t="s" s="2">
-        <v>79</v>
+        <v>356</v>
       </c>
       <c r="AA110" t="s" s="2">
         <v>79</v>
@@ -14456,7 +14401,7 @@
         <v>79</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>77</v>
@@ -14482,10 +14427,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -14508,16 +14453,16 @@
         <v>89</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>102</v>
+        <v>195</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="O111" s="2"/>
       <c r="P111" t="s" s="2">
@@ -14567,7 +14512,7 @@
         <v>79</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>77</v>
@@ -14591,48 +14536,46 @@
         <v>79</v>
       </c>
     </row>
-    <row r="112">
+    <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
-        <v>536</v>
+        <v>79</v>
       </c>
       <c r="E112" s="2"/>
       <c r="F112" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="G112" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H112" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I112" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="J112" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="I112" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J112" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="K112" t="s" s="2">
-        <v>537</v>
+        <v>102</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>538</v>
+        <v>364</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>539</v>
+        <v>365</v>
       </c>
       <c r="N112" t="s" s="2">
-        <v>540</v>
-      </c>
-      <c r="O112" t="s" s="2">
-        <v>541</v>
-      </c>
+        <v>366</v>
+      </c>
+      <c r="O112" s="2"/>
       <c r="P112" t="s" s="2">
         <v>79</v>
       </c>
@@ -14680,13 +14623,13 @@
         <v>79</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>535</v>
+        <v>367</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH112" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AI112" t="s" s="2">
         <v>79</v>
@@ -14698,7 +14641,7 @@
         <v>79</v>
       </c>
       <c r="AL112" t="s" s="2">
-        <v>542</v>
+        <v>79</v>
       </c>
       <c r="AM112" t="s" s="2">
         <v>79</v>
@@ -14706,10 +14649,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>543</v>
+        <v>534</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>543</v>
+        <v>534</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -14720,7 +14663,7 @@
         <v>77</v>
       </c>
       <c r="G113" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H113" t="s" s="2">
         <v>79</v>
@@ -14732,15 +14675,17 @@
         <v>79</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>102</v>
+        <v>535</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>103</v>
+        <v>536</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="N113" s="2"/>
+        <v>537</v>
+      </c>
+      <c r="N113" t="s" s="2">
+        <v>538</v>
+      </c>
       <c r="O113" s="2"/>
       <c r="P113" t="s" s="2">
         <v>79</v>
@@ -14789,19 +14734,19 @@
         <v>79</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>105</v>
+        <v>534</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH113" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AI113" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ113" t="s" s="2">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="AK113" t="s" s="2">
         <v>79</v>
@@ -14815,14 +14760,14 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>544</v>
+        <v>539</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>544</v>
+        <v>539</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
-        <v>107</v>
+        <v>540</v>
       </c>
       <c r="E114" s="2"/>
       <c r="F114" t="s" s="2">
@@ -14838,21 +14783,21 @@
         <v>79</v>
       </c>
       <c r="J114" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>108</v>
+        <v>541</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>109</v>
+        <v>542</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="N114" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="O114" s="2"/>
+        <v>543</v>
+      </c>
+      <c r="N114" s="2"/>
+      <c r="O114" t="s" s="2">
+        <v>544</v>
+      </c>
       <c r="P114" t="s" s="2">
         <v>79</v>
       </c>
@@ -14888,19 +14833,19 @@
         <v>79</v>
       </c>
       <c r="AB114" t="s" s="2">
-        <v>112</v>
+        <v>79</v>
       </c>
       <c r="AC114" t="s" s="2">
-        <v>113</v>
+        <v>79</v>
       </c>
       <c r="AD114" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE114" t="s" s="2">
-        <v>114</v>
+        <v>79</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>115</v>
+        <v>539</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>77</v>
@@ -14912,24 +14857,24 @@
         <v>79</v>
       </c>
       <c r="AJ114" t="s" s="2">
-        <v>116</v>
+        <v>100</v>
       </c>
       <c r="AK114" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL114" t="s" s="2">
-        <v>79</v>
+        <v>545</v>
       </c>
       <c r="AM114" t="s" s="2">
         <v>79</v>
       </c>
     </row>
-    <row r="115">
+    <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -14943,26 +14888,24 @@
         <v>88</v>
       </c>
       <c r="H115" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="I115" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J115" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="K115" t="s" s="2">
         <v>102</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>346</v>
+        <v>103</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>347</v>
-      </c>
-      <c r="N115" t="s" s="2">
-        <v>348</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="N115" s="2"/>
       <c r="O115" s="2"/>
       <c r="P115" t="s" s="2">
         <v>79</v>
@@ -15011,7 +14954,7 @@
         <v>79</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>349</v>
+        <v>105</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>77</v>
@@ -15020,10 +14963,10 @@
         <v>88</v>
       </c>
       <c r="AI115" t="s" s="2">
-        <v>350</v>
+        <v>79</v>
       </c>
       <c r="AJ115" t="s" s="2">
-        <v>100</v>
+        <v>79</v>
       </c>
       <c r="AK115" t="s" s="2">
         <v>79</v>
@@ -15037,21 +14980,21 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
-        <v>79</v>
+        <v>107</v>
       </c>
       <c r="E116" s="2"/>
       <c r="F116" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G116" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H116" t="s" s="2">
         <v>79</v>
@@ -15060,19 +15003,19 @@
         <v>79</v>
       </c>
       <c r="J116" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>129</v>
+        <v>108</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>352</v>
+        <v>109</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>353</v>
+        <v>110</v>
       </c>
       <c r="N116" t="s" s="2">
-        <v>354</v>
+        <v>111</v>
       </c>
       <c r="O116" s="2"/>
       <c r="P116" t="s" s="2">
@@ -15098,13 +15041,13 @@
         <v>79</v>
       </c>
       <c r="X116" t="s" s="2">
-        <v>145</v>
+        <v>79</v>
       </c>
       <c r="Y116" t="s" s="2">
-        <v>355</v>
+        <v>79</v>
       </c>
       <c r="Z116" t="s" s="2">
-        <v>356</v>
+        <v>79</v>
       </c>
       <c r="AA116" t="s" s="2">
         <v>79</v>
@@ -15122,19 +15065,19 @@
         <v>79</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>357</v>
+        <v>115</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH116" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AI116" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ116" t="s" s="2">
-        <v>100</v>
+        <v>116</v>
       </c>
       <c r="AK116" t="s" s="2">
         <v>79</v>
@@ -15148,44 +15091,46 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
-        <v>79</v>
+        <v>549</v>
       </c>
       <c r="E117" s="2"/>
       <c r="F117" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G117" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H117" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I117" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="J117" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>195</v>
+        <v>108</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>359</v>
+        <v>550</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>360</v>
+        <v>551</v>
       </c>
       <c r="N117" t="s" s="2">
-        <v>361</v>
-      </c>
-      <c r="O117" s="2"/>
+        <v>111</v>
+      </c>
+      <c r="O117" t="s" s="2">
+        <v>191</v>
+      </c>
       <c r="P117" t="s" s="2">
         <v>79</v>
       </c>
@@ -15233,19 +15178,19 @@
         <v>79</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>362</v>
+        <v>552</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH117" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AI117" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ117" t="s" s="2">
-        <v>100</v>
+        <v>116</v>
       </c>
       <c r="AK117" t="s" s="2">
         <v>79</v>
@@ -15259,10 +15204,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>548</v>
+        <v>553</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>548</v>
+        <v>553</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -15282,21 +15227,23 @@
         <v>79</v>
       </c>
       <c r="J118" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="K118" t="s" s="2">
         <v>102</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>364</v>
+        <v>554</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>365</v>
+        <v>555</v>
       </c>
       <c r="N118" t="s" s="2">
-        <v>366</v>
-      </c>
-      <c r="O118" s="2"/>
+        <v>556</v>
+      </c>
+      <c r="O118" t="s" s="2">
+        <v>557</v>
+      </c>
       <c r="P118" t="s" s="2">
         <v>79</v>
       </c>
@@ -15344,7 +15291,7 @@
         <v>79</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>367</v>
+        <v>553</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>77</v>
@@ -15370,10 +15317,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>549</v>
+        <v>558</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>549</v>
+        <v>558</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -15381,10 +15328,10 @@
       </c>
       <c r="E119" s="2"/>
       <c r="F119" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="G119" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H119" t="s" s="2">
         <v>79</v>
@@ -15393,20 +15340,18 @@
         <v>79</v>
       </c>
       <c r="J119" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>550</v>
+        <v>559</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>551</v>
+        <v>560</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>552</v>
-      </c>
-      <c r="N119" t="s" s="2">
-        <v>553</v>
-      </c>
+        <v>561</v>
+      </c>
+      <c r="N119" s="2"/>
       <c r="O119" s="2"/>
       <c r="P119" t="s" s="2">
         <v>79</v>
@@ -15455,13 +15400,13 @@
         <v>79</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>549</v>
+        <v>558</v>
       </c>
       <c r="AG119" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="AH119" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AI119" t="s" s="2">
         <v>79</v>
@@ -15479,45 +15424,45 @@
         <v>79</v>
       </c>
     </row>
-    <row r="120" hidden="true">
+    <row r="120">
       <c r="A120" t="s" s="2">
-        <v>554</v>
+        <v>562</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>554</v>
+        <v>562</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
-        <v>555</v>
+        <v>563</v>
       </c>
       <c r="E120" s="2"/>
       <c r="F120" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G120" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H120" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="I120" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J120" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>556</v>
+        <v>102</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>557</v>
+        <v>564</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>558</v>
+        <v>565</v>
       </c>
       <c r="N120" s="2"/>
       <c r="O120" t="s" s="2">
-        <v>559</v>
+        <v>566</v>
       </c>
       <c r="P120" t="s" s="2">
         <v>79</v>
@@ -15566,13 +15511,13 @@
         <v>79</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>554</v>
+        <v>562</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH120" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AI120" t="s" s="2">
         <v>79</v>
@@ -15584,7 +15529,7 @@
         <v>79</v>
       </c>
       <c r="AL120" t="s" s="2">
-        <v>560</v>
+        <v>567</v>
       </c>
       <c r="AM120" t="s" s="2">
         <v>79</v>
@@ -15592,10 +15537,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>561</v>
+        <v>568</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>561</v>
+        <v>568</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -15606,7 +15551,7 @@
         <v>77</v>
       </c>
       <c r="G121" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H121" t="s" s="2">
         <v>79</v>
@@ -15618,13 +15563,13 @@
         <v>79</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>102</v>
+        <v>225</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>103</v>
+        <v>569</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>104</v>
+        <v>570</v>
       </c>
       <c r="N121" s="2"/>
       <c r="O121" s="2"/>
@@ -15651,13 +15596,13 @@
         <v>79</v>
       </c>
       <c r="X121" t="s" s="2">
-        <v>79</v>
+        <v>153</v>
       </c>
       <c r="Y121" t="s" s="2">
-        <v>79</v>
+        <v>571</v>
       </c>
       <c r="Z121" t="s" s="2">
-        <v>79</v>
+        <v>572</v>
       </c>
       <c r="AA121" t="s" s="2">
         <v>79</v>
@@ -15675,25 +15620,25 @@
         <v>79</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>105</v>
+        <v>568</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH121" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AI121" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ121" t="s" s="2">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="AK121" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL121" t="s" s="2">
-        <v>79</v>
+        <v>567</v>
       </c>
       <c r="AM121" t="s" s="2">
         <v>79</v>
@@ -15701,14 +15646,14 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>562</v>
+        <v>573</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>562</v>
+        <v>573</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
-        <v>107</v>
+        <v>79</v>
       </c>
       <c r="E122" s="2"/>
       <c r="F122" t="s" s="2">
@@ -15727,18 +15672,20 @@
         <v>79</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>108</v>
+        <v>574</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>109</v>
+        <v>575</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>110</v>
+        <v>576</v>
       </c>
       <c r="N122" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="O122" s="2"/>
+        <v>577</v>
+      </c>
+      <c r="O122" t="s" s="2">
+        <v>578</v>
+      </c>
       <c r="P122" t="s" s="2">
         <v>79</v>
       </c>
@@ -15786,7 +15733,7 @@
         <v>79</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>115</v>
+        <v>573</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>77</v>
@@ -15798,688 +15745,20 @@
         <v>79</v>
       </c>
       <c r="AJ122" t="s" s="2">
-        <v>116</v>
+        <v>100</v>
       </c>
       <c r="AK122" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL122" t="s" s="2">
-        <v>79</v>
+        <v>567</v>
       </c>
       <c r="AM122" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="123" hidden="true">
-      <c r="A123" t="s" s="2">
-        <v>563</v>
-      </c>
-      <c r="B123" t="s" s="2">
-        <v>563</v>
-      </c>
-      <c r="C123" s="2"/>
-      <c r="D123" t="s" s="2">
-        <v>564</v>
-      </c>
-      <c r="E123" s="2"/>
-      <c r="F123" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="G123" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H123" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I123" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="J123" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="K123" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="L123" t="s" s="2">
-        <v>565</v>
-      </c>
-      <c r="M123" t="s" s="2">
-        <v>566</v>
-      </c>
-      <c r="N123" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="O123" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="P123" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q123" s="2"/>
-      <c r="R123" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S123" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T123" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U123" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V123" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W123" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X123" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y123" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z123" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA123" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB123" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC123" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD123" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE123" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF123" t="s" s="2">
-        <v>567</v>
-      </c>
-      <c r="AG123" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH123" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI123" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ123" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="AK123" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL123" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM123" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="124" hidden="true">
-      <c r="A124" t="s" s="2">
-        <v>568</v>
-      </c>
-      <c r="B124" t="s" s="2">
-        <v>568</v>
-      </c>
-      <c r="C124" s="2"/>
-      <c r="D124" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E124" s="2"/>
-      <c r="F124" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="G124" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H124" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I124" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J124" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K124" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="L124" t="s" s="2">
-        <v>569</v>
-      </c>
-      <c r="M124" t="s" s="2">
-        <v>570</v>
-      </c>
-      <c r="N124" t="s" s="2">
-        <v>571</v>
-      </c>
-      <c r="O124" t="s" s="2">
-        <v>572</v>
-      </c>
-      <c r="P124" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q124" s="2"/>
-      <c r="R124" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S124" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T124" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U124" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V124" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W124" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X124" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y124" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z124" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA124" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB124" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC124" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD124" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE124" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF124" t="s" s="2">
-        <v>568</v>
-      </c>
-      <c r="AG124" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH124" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI124" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ124" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK124" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL124" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM124" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="125" hidden="true">
-      <c r="A125" t="s" s="2">
-        <v>573</v>
-      </c>
-      <c r="B125" t="s" s="2">
-        <v>573</v>
-      </c>
-      <c r="C125" s="2"/>
-      <c r="D125" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E125" s="2"/>
-      <c r="F125" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="G125" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H125" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I125" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J125" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="K125" t="s" s="2">
-        <v>574</v>
-      </c>
-      <c r="L125" t="s" s="2">
-        <v>575</v>
-      </c>
-      <c r="M125" t="s" s="2">
-        <v>576</v>
-      </c>
-      <c r="N125" s="2"/>
-      <c r="O125" s="2"/>
-      <c r="P125" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q125" s="2"/>
-      <c r="R125" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S125" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T125" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U125" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V125" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W125" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X125" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y125" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z125" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA125" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB125" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC125" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD125" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE125" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF125" t="s" s="2">
-        <v>573</v>
-      </c>
-      <c r="AG125" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AH125" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI125" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ125" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK125" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL125" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AM125" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="s" s="2">
-        <v>577</v>
-      </c>
-      <c r="B126" t="s" s="2">
-        <v>577</v>
-      </c>
-      <c r="C126" s="2"/>
-      <c r="D126" t="s" s="2">
-        <v>578</v>
-      </c>
-      <c r="E126" s="2"/>
-      <c r="F126" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="G126" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H126" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="I126" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J126" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K126" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="L126" t="s" s="2">
-        <v>579</v>
-      </c>
-      <c r="M126" t="s" s="2">
-        <v>580</v>
-      </c>
-      <c r="N126" s="2"/>
-      <c r="O126" t="s" s="2">
-        <v>581</v>
-      </c>
-      <c r="P126" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q126" s="2"/>
-      <c r="R126" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S126" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T126" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U126" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V126" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W126" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X126" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y126" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z126" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA126" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB126" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC126" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD126" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE126" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF126" t="s" s="2">
-        <v>577</v>
-      </c>
-      <c r="AG126" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH126" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI126" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ126" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK126" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL126" t="s" s="2">
-        <v>582</v>
-      </c>
-      <c r="AM126" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="127" hidden="true">
-      <c r="A127" t="s" s="2">
-        <v>583</v>
-      </c>
-      <c r="B127" t="s" s="2">
-        <v>583</v>
-      </c>
-      <c r="C127" s="2"/>
-      <c r="D127" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E127" s="2"/>
-      <c r="F127" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="G127" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H127" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I127" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J127" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K127" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="L127" t="s" s="2">
-        <v>584</v>
-      </c>
-      <c r="M127" t="s" s="2">
-        <v>585</v>
-      </c>
-      <c r="N127" s="2"/>
-      <c r="O127" s="2"/>
-      <c r="P127" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q127" s="2"/>
-      <c r="R127" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S127" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T127" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U127" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V127" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W127" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X127" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="Y127" t="s" s="2">
-        <v>586</v>
-      </c>
-      <c r="Z127" t="s" s="2">
-        <v>587</v>
-      </c>
-      <c r="AA127" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB127" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC127" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD127" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE127" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF127" t="s" s="2">
-        <v>583</v>
-      </c>
-      <c r="AG127" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH127" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI127" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ127" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK127" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL127" t="s" s="2">
-        <v>582</v>
-      </c>
-      <c r="AM127" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="128" hidden="true">
-      <c r="A128" t="s" s="2">
-        <v>588</v>
-      </c>
-      <c r="B128" t="s" s="2">
-        <v>588</v>
-      </c>
-      <c r="C128" s="2"/>
-      <c r="D128" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E128" s="2"/>
-      <c r="F128" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="G128" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H128" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I128" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J128" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K128" t="s" s="2">
-        <v>589</v>
-      </c>
-      <c r="L128" t="s" s="2">
-        <v>590</v>
-      </c>
-      <c r="M128" t="s" s="2">
-        <v>591</v>
-      </c>
-      <c r="N128" t="s" s="2">
-        <v>592</v>
-      </c>
-      <c r="O128" t="s" s="2">
-        <v>593</v>
-      </c>
-      <c r="P128" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q128" s="2"/>
-      <c r="R128" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S128" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T128" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U128" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V128" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W128" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X128" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y128" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z128" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA128" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB128" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC128" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD128" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE128" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF128" t="s" s="2">
-        <v>588</v>
-      </c>
-      <c r="AG128" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH128" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI128" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ128" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK128" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL128" t="s" s="2">
-        <v>582</v>
-      </c>
-      <c r="AM128" t="s" s="2">
         <v>79</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AM128">
+  <autoFilter ref="A1:AM122">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -16489,7 +15768,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI127">
+  <conditionalFormatting sqref="A2:AI121">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/branches/master/StructureDefinition-mii-pr-labor-laborbefund.xlsx
+++ b/branches/master/StructureDefinition-mii-pr-labor-laborbefund.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T20:13:51+00:00</t>
+    <t>2026-09-08T09:14:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-mii-pr-labor-laborbefund.xlsx
+++ b/branches/master/StructureDefinition-mii-pr-labor-laborbefund.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T09:14:04+00:00</t>
+    <t>2026-09-08T11:22:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-mii-pr-labor-laborbefund.xlsx
+++ b/branches/master/StructureDefinition-mii-pr-labor-laborbefund.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot.rc3</t>
+    <t>2027.0.0-ballot.rc4</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T11:22:39+00:00</t>
+    <t>2026-09-08T11:59:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
